--- a/Sheets/12- Dec Salaries 2025.xlsx
+++ b/Sheets/12- Dec Salaries 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude\SalariesSummary\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9F338D-4C65-4C59-9B66-4D324739F2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844C170A-61F5-4AD9-A0DE-599D330E9B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="مرتبات" sheetId="7" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="159">
   <si>
     <t>اجمالي الشركاء</t>
   </si>
@@ -485,12 +485,6 @@
     <t>د/ أحمد بغدادي رشدي محمد</t>
   </si>
   <si>
-    <t>CSH</t>
-  </si>
-  <si>
-    <t>TRF</t>
-  </si>
-  <si>
     <t>أ/ نجوى إبراهيم محمود غنيم</t>
   </si>
   <si>
@@ -515,31 +509,7 @@
     <t>الخروج من التأمينات شهر بعد تاريخ انتهاء العمل</t>
   </si>
   <si>
-    <t>Wife insurance 12/12</t>
-  </si>
-  <si>
-    <t>Last day 11-12-2025</t>
-  </si>
-  <si>
-    <t>unpaid emergency 24-12 and Nov morning late 2 days 19h late</t>
-  </si>
-  <si>
-    <t>unpaid emergency 10-12 and Nov morning late 4 days 30h 26m late</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Nov morning late 4 days 31h 14m late</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Nov morning late 1 day 13h late</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Nov morning late 1 day 12h 13m late</t>
-  </si>
-  <si>
     <t>محمد حسين محمد محمد</t>
-  </si>
-  <si>
-    <t>He joined 21-12-2025</t>
   </si>
   <si>
     <t>مستشار محمد ماهر عبدالواحد</t>
@@ -566,7 +536,7 @@
     <numFmt numFmtId="168" formatCode="[$-20B0000]d\ mmmm\ yyyy;@"/>
     <numFmt numFmtId="169" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -752,13 +722,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="26">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -881,19 +846,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1338,7 +1291,7 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1728,34 +1681,15 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="23" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="28" fillId="3" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="21" fillId="11" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="11" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="28" fillId="22" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="23" fillId="22" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="23" fillId="21" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1765,28 +1699,6 @@
     <xf numFmtId="17" fontId="25" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="31" fillId="23" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="20" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="12" fontId="3" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="20" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="21" fillId="20" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="20" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="20" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1795,32 +1707,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="28" fillId="20" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="28" fillId="24" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="28" fillId="22" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="28" fillId="8" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="25" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="21" fillId="25" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="25" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="25" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="25" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="3" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="12" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="28" fillId="25" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="28" fillId="23" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2705,7 +2599,7 @@
   <cols>
     <col min="1" max="1" width="11.109375" customWidth="1"/>
     <col min="2" max="2" width="39.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="3" max="3" width="1.33203125" customWidth="1"/>
     <col min="4" max="4" width="22.77734375" customWidth="1"/>
     <col min="5" max="5" width="21.77734375" customWidth="1"/>
     <col min="6" max="6" width="17.109375" customWidth="1"/>
@@ -2723,7 +2617,7 @@
   <sheetData>
     <row r="1" spans="1:16" s="52" customFormat="1" ht="44.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="130" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B1" s="131"/>
       <c r="C1" s="131"/>
@@ -2747,7 +2641,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="133"/>
-      <c r="D2" s="181">
+      <c r="D2" s="170">
         <v>45870</v>
       </c>
       <c r="E2" s="66"/>
@@ -2769,7 +2663,7 @@
         <v>35</v>
       </c>
       <c r="C3" s="112" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D3" s="113" t="s">
         <v>34</v>
@@ -2822,7 +2716,7 @@
       </c>
       <c r="E4" s="34" t="str">
         <f>HYPERLINK(اضافات!N4)</f>
-        <v>1422</v>
+        <v>0</v>
       </c>
       <c r="F4" s="34" t="str">
         <f>HYPERLINK(اضافات!M4)</f>
@@ -2842,7 +2736,7 @@
       </c>
       <c r="J4" s="150">
         <f>SUM(D4,VALUE(E4),VALUE(F4),VALUE(G4))</f>
-        <v>1422</v>
+        <v>0</v>
       </c>
       <c r="K4" s="150">
         <f>VALUE(D4)+VALUE(G4)+VALUE(H4)-VALUE(I4)</f>
@@ -2862,16 +2756,16 @@
         <v>129</v>
       </c>
       <c r="C5" s="25"/>
-      <c r="D5" s="151">
-        <v>500000</v>
+      <c r="D5" s="148">
+        <v>0</v>
       </c>
       <c r="E5" s="34" t="str">
         <f>HYPERLINK(اضافات!N5)</f>
-        <v>159776</v>
+        <v>0</v>
       </c>
       <c r="F5" s="34" t="str">
         <f>HYPERLINK(اضافات!M5)</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G5" s="34" t="str">
         <f>HYPERLINK(اضافات!F5)</f>
@@ -2885,13 +2779,13 @@
         <f>HYPERLINK(خصومات!L5)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="164">
+      <c r="J5" s="163">
         <f t="shared" ref="J5:J68" si="0">SUM(D5,VALUE(E5),VALUE(F5),VALUE(G5))</f>
-        <v>660776</v>
-      </c>
-      <c r="K5" s="164">
+        <v>0</v>
+      </c>
+      <c r="K5" s="163">
         <f t="shared" ref="K5:K68" si="1">VALUE(D5)+VALUE(G5)+VALUE(H5)-VALUE(I5)</f>
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="L5" s="26"/>
       <c r="M5" s="28"/>
@@ -2907,16 +2801,16 @@
         <v>130</v>
       </c>
       <c r="C6" s="25"/>
-      <c r="D6" s="151">
-        <v>120000</v>
+      <c r="D6" s="148">
+        <v>0</v>
       </c>
       <c r="E6" s="34" t="str">
         <f>HYPERLINK(اضافات!N6)</f>
-        <v>36051</v>
+        <v>0</v>
       </c>
       <c r="F6" s="34" t="str">
         <f>HYPERLINK(اضافات!M6)</f>
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="G6" s="34" t="str">
         <f>HYPERLINK(اضافات!F6)</f>
@@ -2930,13 +2824,13 @@
         <f>HYPERLINK(خصومات!L6)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="164">
+      <c r="J6" s="163">
         <f t="shared" si="0"/>
-        <v>156526</v>
-      </c>
-      <c r="K6" s="164">
+        <v>0</v>
+      </c>
+      <c r="K6" s="163">
         <f t="shared" si="1"/>
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="L6" s="26"/>
       <c r="M6" s="28"/>
@@ -3427,7 +3321,7 @@
       <c r="C18" s="119"/>
       <c r="D18" s="152">
         <f>SUM(D4:D17)</f>
-        <v>620000</v>
+        <v>0</v>
       </c>
       <c r="E18" s="120">
         <f t="shared" ref="E18:K18" si="2">SUM(E4:E17)</f>
@@ -3451,15 +3345,15 @@
       </c>
       <c r="J18" s="152">
         <f t="shared" si="2"/>
-        <v>818724</v>
+        <v>0</v>
       </c>
       <c r="K18" s="152">
         <f t="shared" si="2"/>
-        <v>620000</v>
+        <v>0</v>
       </c>
       <c r="L18" s="120">
         <f>SUM(K4:K17)</f>
-        <v>620000</v>
+        <v>0</v>
       </c>
       <c r="M18" s="121"/>
       <c r="N18" s="122"/>
@@ -3474,12 +3368,12 @@
         <v>78</v>
       </c>
       <c r="C19" s="25"/>
-      <c r="D19" s="151">
-        <v>46300</v>
+      <c r="D19" s="148">
+        <v>0</v>
       </c>
       <c r="E19" s="34" t="str">
         <f>HYPERLINK(اضافات!N19)</f>
-        <v>11326</v>
+        <v>0</v>
       </c>
       <c r="F19" s="34" t="str">
         <f>HYPERLINK(اضافات!M19)</f>
@@ -3497,13 +3391,13 @@
         <f>HYPERLINK(خصومات!L19)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="164">
+      <c r="J19" s="163">
         <f t="shared" si="0"/>
-        <v>57626</v>
-      </c>
-      <c r="K19" s="164">
+        <v>0</v>
+      </c>
+      <c r="K19" s="163">
         <f t="shared" si="1"/>
-        <v>46300</v>
+        <v>0</v>
       </c>
       <c r="L19" s="26"/>
       <c r="M19" s="28"/>
@@ -3519,16 +3413,16 @@
         <v>64</v>
       </c>
       <c r="C20" s="25"/>
-      <c r="D20" s="151">
-        <v>34500</v>
+      <c r="D20" s="148">
+        <v>0</v>
       </c>
       <c r="E20" s="34" t="str">
         <f>HYPERLINK(اضافات!N20)</f>
-        <v>7988</v>
+        <v>0</v>
       </c>
       <c r="F20" s="34" t="str">
         <f>HYPERLINK(اضافات!M20)</f>
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="G20" s="34" t="str">
         <f>HYPERLINK(اضافات!F20)</f>
@@ -3540,15 +3434,15 @@
       </c>
       <c r="I20" s="93" t="str">
         <f>HYPERLINK(خصومات!L20)</f>
-        <v>313</v>
-      </c>
-      <c r="J20" s="164">
+        <v>0</v>
+      </c>
+      <c r="J20" s="163">
         <f t="shared" si="0"/>
-        <v>42963</v>
-      </c>
-      <c r="K20" s="164">
+        <v>0</v>
+      </c>
+      <c r="K20" s="163">
         <f t="shared" si="1"/>
-        <v>34187</v>
+        <v>0</v>
       </c>
       <c r="L20" s="26"/>
       <c r="M20" s="28"/>
@@ -3564,12 +3458,12 @@
         <v>91</v>
       </c>
       <c r="C21" s="25"/>
-      <c r="D21" s="151">
-        <v>51750</v>
+      <c r="D21" s="148">
+        <v>0</v>
       </c>
       <c r="E21" s="34" t="str">
         <f>HYPERLINK(اضافات!N21)</f>
-        <v>13290</v>
+        <v>0</v>
       </c>
       <c r="F21" s="34" t="str">
         <f>HYPERLINK(اضافات!M21)</f>
@@ -3587,13 +3481,13 @@
         <f>HYPERLINK(خصومات!L21)</f>
         <v>0</v>
       </c>
-      <c r="J21" s="164">
+      <c r="J21" s="163">
         <f t="shared" si="0"/>
-        <v>65040</v>
-      </c>
-      <c r="K21" s="164">
+        <v>0</v>
+      </c>
+      <c r="K21" s="163">
         <f t="shared" si="1"/>
-        <v>51750</v>
+        <v>0</v>
       </c>
       <c r="L21" s="26"/>
       <c r="M21" s="28"/>
@@ -3609,12 +3503,12 @@
         <v>65</v>
       </c>
       <c r="C22" s="25"/>
-      <c r="D22" s="166">
-        <v>69000</v>
+      <c r="D22" s="148">
+        <v>0</v>
       </c>
       <c r="E22" s="34" t="str">
         <f>HYPERLINK(اضافات!N22)</f>
-        <v>14450</v>
+        <v>0</v>
       </c>
       <c r="F22" s="34" t="str">
         <f>HYPERLINK(اضافات!M22)</f>
@@ -3630,15 +3524,15 @@
       </c>
       <c r="I22" s="93" t="str">
         <f>HYPERLINK(خصومات!L22)</f>
-        <v>7100</v>
-      </c>
-      <c r="J22" s="164">
+        <v>0</v>
+      </c>
+      <c r="J22" s="163">
         <f t="shared" si="0"/>
-        <v>83450</v>
-      </c>
-      <c r="K22" s="164">
+        <v>0</v>
+      </c>
+      <c r="K22" s="163">
         <f t="shared" si="1"/>
-        <v>61900</v>
+        <v>0</v>
       </c>
       <c r="L22" s="26"/>
       <c r="M22" s="28"/>
@@ -3654,12 +3548,12 @@
         <v>68</v>
       </c>
       <c r="C23" s="25"/>
-      <c r="D23" s="151">
-        <v>55000</v>
+      <c r="D23" s="148">
+        <v>0</v>
       </c>
       <c r="E23" s="34" t="str">
         <f>HYPERLINK(اضافات!N23)</f>
-        <v>14116</v>
+        <v>0</v>
       </c>
       <c r="F23" s="34" t="str">
         <f>HYPERLINK(اضافات!M23)</f>
@@ -3677,13 +3571,13 @@
         <f>HYPERLINK(خصومات!L23)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="164">
+      <c r="J23" s="163">
         <f t="shared" si="0"/>
-        <v>69116</v>
-      </c>
-      <c r="K23" s="164">
+        <v>0</v>
+      </c>
+      <c r="K23" s="163">
         <f t="shared" si="1"/>
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="L23" s="26"/>
       <c r="M23" s="28"/>
@@ -3699,12 +3593,12 @@
         <v>127</v>
       </c>
       <c r="C24" s="25"/>
-      <c r="D24" s="151">
-        <v>60000</v>
+      <c r="D24" s="148">
+        <v>0</v>
       </c>
       <c r="E24" s="34" t="str">
         <f>HYPERLINK(اضافات!N24)</f>
-        <v>11891</v>
+        <v>0</v>
       </c>
       <c r="F24" s="34" t="str">
         <f>HYPERLINK(اضافات!M24)</f>
@@ -3720,15 +3614,15 @@
       </c>
       <c r="I24" s="93" t="str">
         <f>HYPERLINK(خصومات!L24)</f>
-        <v>2000</v>
-      </c>
-      <c r="J24" s="164">
+        <v>0</v>
+      </c>
+      <c r="J24" s="163">
         <f t="shared" si="0"/>
-        <v>71891</v>
-      </c>
-      <c r="K24" s="164">
+        <v>0</v>
+      </c>
+      <c r="K24" s="163">
         <f t="shared" si="1"/>
-        <v>58000</v>
+        <v>0</v>
       </c>
       <c r="L24" s="26"/>
       <c r="M24" s="28"/>
@@ -3744,16 +3638,16 @@
         <v>66</v>
       </c>
       <c r="C25" s="25"/>
-      <c r="D25" s="151">
-        <v>34500</v>
+      <c r="D25" s="148">
+        <v>0</v>
       </c>
       <c r="E25" s="34" t="str">
         <f>HYPERLINK(اضافات!N25)</f>
-        <v>7945</v>
+        <v>0</v>
       </c>
       <c r="F25" s="34" t="str">
         <f>HYPERLINK(اضافات!M25)</f>
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="G25" s="34" t="str">
         <f>HYPERLINK(اضافات!F25)</f>
@@ -3765,15 +3659,15 @@
       </c>
       <c r="I25" s="93" t="str">
         <f>HYPERLINK(خصومات!L25)</f>
-        <v>687</v>
-      </c>
-      <c r="J25" s="164">
+        <v>0</v>
+      </c>
+      <c r="J25" s="163">
         <f t="shared" si="0"/>
-        <v>42920</v>
-      </c>
-      <c r="K25" s="164">
+        <v>0</v>
+      </c>
+      <c r="K25" s="163">
         <f t="shared" si="1"/>
-        <v>33813</v>
+        <v>0</v>
       </c>
       <c r="L25" s="26"/>
       <c r="M25" s="28"/>
@@ -3787,7 +3681,7 @@
         <v>82</v>
       </c>
       <c r="C26" s="25"/>
-      <c r="D26" s="151">
+      <c r="D26" s="148">
         <v>0</v>
       </c>
       <c r="E26" s="34" t="str">
@@ -3810,11 +3704,11 @@
         <f>HYPERLINK(خصومات!L26)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="164">
+      <c r="J26" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K26" s="164">
+      <c r="K26" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3830,7 +3724,7 @@
         <v>82</v>
       </c>
       <c r="C27" s="25"/>
-      <c r="D27" s="151">
+      <c r="D27" s="148">
         <v>0</v>
       </c>
       <c r="E27" s="34" t="str">
@@ -3853,11 +3747,11 @@
         <f>HYPERLINK(خصومات!L27)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="164">
+      <c r="J27" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K27" s="164">
+      <c r="K27" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3873,7 +3767,7 @@
         <v>82</v>
       </c>
       <c r="C28" s="25"/>
-      <c r="D28" s="151">
+      <c r="D28" s="148">
         <v>0</v>
       </c>
       <c r="E28" s="34" t="str">
@@ -3896,11 +3790,11 @@
         <f>HYPERLINK(خصومات!L28)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="164">
+      <c r="J28" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K28" s="164">
+      <c r="K28" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3916,7 +3810,7 @@
         <v>82</v>
       </c>
       <c r="C29" s="25"/>
-      <c r="D29" s="151">
+      <c r="D29" s="148">
         <v>0</v>
       </c>
       <c r="E29" s="34" t="str">
@@ -3939,11 +3833,11 @@
         <f>HYPERLINK(خصومات!L29)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="164">
+      <c r="J29" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K29" s="164">
+      <c r="K29" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3959,7 +3853,7 @@
         <v>82</v>
       </c>
       <c r="C30" s="78"/>
-      <c r="D30" s="151">
+      <c r="D30" s="148">
         <v>0</v>
       </c>
       <c r="E30" s="34" t="str">
@@ -3982,11 +3876,11 @@
         <f>HYPERLINK(خصومات!L30)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="164">
+      <c r="J30" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K30" s="164">
+      <c r="K30" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4002,7 +3896,7 @@
         <v>82</v>
       </c>
       <c r="C31" s="25"/>
-      <c r="D31" s="151">
+      <c r="D31" s="148">
         <v>0</v>
       </c>
       <c r="E31" s="34" t="str">
@@ -4025,11 +3919,11 @@
         <f>HYPERLINK(خصومات!L31)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="164">
+      <c r="J31" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K31" s="164">
+      <c r="K31" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4045,7 +3939,7 @@
         <v>82</v>
       </c>
       <c r="C32" s="25"/>
-      <c r="D32" s="151">
+      <c r="D32" s="148">
         <v>0</v>
       </c>
       <c r="E32" s="34" t="str">
@@ -4068,11 +3962,11 @@
         <f>HYPERLINK(خصومات!L32)</f>
         <v>0</v>
       </c>
-      <c r="J32" s="164">
+      <c r="J32" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K32" s="164">
+      <c r="K32" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4090,12 +3984,12 @@
         <v>83</v>
       </c>
       <c r="C33" s="30"/>
-      <c r="D33" s="151">
-        <v>40250</v>
+      <c r="D33" s="148">
+        <v>0</v>
       </c>
       <c r="E33" s="34" t="str">
         <f>HYPERLINK(اضافات!N33)</f>
-        <v>14100</v>
+        <v>0</v>
       </c>
       <c r="F33" s="34" t="str">
         <f>HYPERLINK(اضافات!M33)</f>
@@ -4113,13 +4007,13 @@
         <f>HYPERLINK(خصومات!L33)</f>
         <v>0</v>
       </c>
-      <c r="J33" s="164">
+      <c r="J33" s="163">
         <f t="shared" si="0"/>
-        <v>54350</v>
-      </c>
-      <c r="K33" s="164">
+        <v>0</v>
+      </c>
+      <c r="K33" s="163">
         <f t="shared" si="1"/>
-        <v>40250</v>
+        <v>0</v>
       </c>
       <c r="L33" s="32"/>
       <c r="M33" s="28"/>
@@ -4135,16 +4029,16 @@
         <v>67</v>
       </c>
       <c r="C34" s="30"/>
-      <c r="D34" s="151">
-        <v>14500</v>
+      <c r="D34" s="148">
+        <v>0</v>
       </c>
       <c r="E34" s="34" t="str">
         <f>HYPERLINK(اضافات!N34)</f>
-        <v>2824</v>
+        <v>0</v>
       </c>
       <c r="F34" s="34" t="str">
         <f>HYPERLINK(اضافات!M34)</f>
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="G34" s="34" t="str">
         <f>HYPERLINK(اضافات!F34)</f>
@@ -4158,13 +4052,13 @@
         <f>HYPERLINK(خصومات!L34)</f>
         <v>0</v>
       </c>
-      <c r="J34" s="164">
+      <c r="J34" s="163">
         <f t="shared" si="0"/>
-        <v>17639</v>
-      </c>
-      <c r="K34" s="164">
+        <v>0</v>
+      </c>
+      <c r="K34" s="163">
         <f t="shared" si="1"/>
-        <v>14500</v>
+        <v>0</v>
       </c>
       <c r="L34" s="32"/>
       <c r="M34" s="28"/>
@@ -4180,12 +4074,12 @@
         <v>136</v>
       </c>
       <c r="C35" s="30"/>
-      <c r="D35" s="151">
-        <v>14000</v>
+      <c r="D35" s="148">
+        <v>0</v>
       </c>
       <c r="E35" s="34" t="str">
         <f>HYPERLINK(اضافات!N35)</f>
-        <v>2518</v>
+        <v>0</v>
       </c>
       <c r="F35" s="34" t="str">
         <f>HYPERLINK(اضافات!M35)</f>
@@ -4203,13 +4097,13 @@
         <f>HYPERLINK(خصومات!L35)</f>
         <v>0</v>
       </c>
-      <c r="J35" s="164">
+      <c r="J35" s="163">
         <f t="shared" si="0"/>
-        <v>16518</v>
-      </c>
-      <c r="K35" s="164">
+        <v>0</v>
+      </c>
+      <c r="K35" s="163">
         <f t="shared" si="1"/>
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="L35" s="32"/>
       <c r="M35" s="28"/>
@@ -4223,7 +4117,7 @@
         <v>82</v>
       </c>
       <c r="C36" s="30"/>
-      <c r="D36" s="151">
+      <c r="D36" s="148">
         <v>0</v>
       </c>
       <c r="E36" s="34" t="str">
@@ -4246,11 +4140,11 @@
         <f>HYPERLINK(خصومات!L36)</f>
         <v>0</v>
       </c>
-      <c r="J36" s="164">
+      <c r="J36" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K36" s="164">
+      <c r="K36" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4266,7 +4160,7 @@
         <v>82</v>
       </c>
       <c r="C37" s="30"/>
-      <c r="D37" s="151">
+      <c r="D37" s="148">
         <v>0</v>
       </c>
       <c r="E37" s="34" t="str">
@@ -4289,11 +4183,11 @@
         <f>HYPERLINK(خصومات!L37)</f>
         <v>0</v>
       </c>
-      <c r="J37" s="164">
+      <c r="J37" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K37" s="164">
+      <c r="K37" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4309,7 +4203,7 @@
         <v>82</v>
       </c>
       <c r="C38" s="30"/>
-      <c r="D38" s="151">
+      <c r="D38" s="148">
         <v>0</v>
       </c>
       <c r="E38" s="34" t="str">
@@ -4332,11 +4226,11 @@
         <f>HYPERLINK(خصومات!L38)</f>
         <v>0</v>
       </c>
-      <c r="J38" s="164">
+      <c r="J38" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K38" s="164">
+      <c r="K38" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4352,7 +4246,7 @@
         <v>82</v>
       </c>
       <c r="C39" s="30"/>
-      <c r="D39" s="151">
+      <c r="D39" s="148">
         <v>0</v>
       </c>
       <c r="E39" s="34" t="str">
@@ -4375,11 +4269,11 @@
         <f>HYPERLINK(خصومات!L39)</f>
         <v>0</v>
       </c>
-      <c r="J39" s="164">
+      <c r="J39" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K39" s="164">
+      <c r="K39" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4395,7 +4289,7 @@
         <v>82</v>
       </c>
       <c r="C40" s="30"/>
-      <c r="D40" s="151">
+      <c r="D40" s="148">
         <v>0</v>
       </c>
       <c r="E40" s="34" t="str">
@@ -4418,11 +4312,11 @@
         <f>HYPERLINK(خصومات!L40)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="164">
+      <c r="J40" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K40" s="164">
+      <c r="K40" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4438,7 +4332,7 @@
         <v>82</v>
       </c>
       <c r="C41" s="30"/>
-      <c r="D41" s="151">
+      <c r="D41" s="148">
         <v>0</v>
       </c>
       <c r="E41" s="34" t="str">
@@ -4461,11 +4355,11 @@
         <f>HYPERLINK(خصومات!L41)</f>
         <v>0</v>
       </c>
-      <c r="J41" s="164">
+      <c r="J41" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K41" s="164">
+      <c r="K41" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4481,7 +4375,7 @@
         <v>82</v>
       </c>
       <c r="C42" s="30"/>
-      <c r="D42" s="151">
+      <c r="D42" s="148">
         <v>0</v>
       </c>
       <c r="E42" s="34" t="str">
@@ -4504,11 +4398,11 @@
         <f>HYPERLINK(خصومات!L42)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="164">
+      <c r="J42" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K42" s="164">
+      <c r="K42" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4524,7 +4418,7 @@
         <v>82</v>
       </c>
       <c r="C43" s="30"/>
-      <c r="D43" s="151">
+      <c r="D43" s="148">
         <v>0</v>
       </c>
       <c r="E43" s="34" t="str">
@@ -4547,11 +4441,11 @@
         <f>HYPERLINK(خصومات!L43)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="164">
+      <c r="J43" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K43" s="164">
+      <c r="K43" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4567,7 +4461,7 @@
         <v>82</v>
       </c>
       <c r="C44" s="30"/>
-      <c r="D44" s="151">
+      <c r="D44" s="148">
         <v>0</v>
       </c>
       <c r="E44" s="34" t="str">
@@ -4590,11 +4484,11 @@
         <f>HYPERLINK(خصومات!L44)</f>
         <v>0</v>
       </c>
-      <c r="J44" s="164">
+      <c r="J44" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K44" s="164">
+      <c r="K44" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4612,12 +4506,12 @@
         <v>124</v>
       </c>
       <c r="C45" s="30"/>
-      <c r="D45" s="151">
-        <v>11000</v>
+      <c r="D45" s="148">
+        <v>0</v>
       </c>
       <c r="E45" s="34" t="str">
         <f>HYPERLINK(اضافات!N45)</f>
-        <v>1779</v>
+        <v>0</v>
       </c>
       <c r="F45" s="34" t="str">
         <f>HYPERLINK(اضافات!M45)</f>
@@ -4629,19 +4523,19 @@
       </c>
       <c r="H45" s="34" t="str">
         <f>HYPERLINK(اضافات!O45)</f>
-        <v>5250</v>
+        <v>0</v>
       </c>
       <c r="I45" s="93" t="str">
         <f>HYPERLINK(خصومات!L45)</f>
-        <v>1834</v>
-      </c>
-      <c r="J45" s="164">
+        <v>0</v>
+      </c>
+      <c r="J45" s="163">
         <f t="shared" si="0"/>
-        <v>12779</v>
-      </c>
-      <c r="K45" s="164">
+        <v>0</v>
+      </c>
+      <c r="K45" s="163">
         <f t="shared" si="1"/>
-        <v>14416</v>
+        <v>0</v>
       </c>
       <c r="L45" s="32"/>
       <c r="M45" s="28"/>
@@ -4657,12 +4551,12 @@
         <v>133</v>
       </c>
       <c r="C46" s="30"/>
-      <c r="D46" s="151">
-        <v>10000</v>
+      <c r="D46" s="148">
+        <v>0</v>
       </c>
       <c r="E46" s="34" t="str">
         <f>HYPERLINK(اضافات!N46)</f>
-        <v>1655</v>
+        <v>0</v>
       </c>
       <c r="F46" s="34" t="str">
         <f>HYPERLINK(اضافات!M46)</f>
@@ -4678,15 +4572,15 @@
       </c>
       <c r="I46" s="93" t="str">
         <f>HYPERLINK(خصومات!L46)</f>
-        <v>333</v>
-      </c>
-      <c r="J46" s="164">
+        <v>0</v>
+      </c>
+      <c r="J46" s="163">
         <f t="shared" si="0"/>
-        <v>11655</v>
-      </c>
-      <c r="K46" s="164">
+        <v>0</v>
+      </c>
+      <c r="K46" s="163">
         <f t="shared" si="1"/>
-        <v>9667</v>
+        <v>0</v>
       </c>
       <c r="L46" s="32"/>
       <c r="M46" s="28"/>
@@ -4698,40 +4592,40 @@
       <c r="A47" s="31">
         <v>13</v>
       </c>
-      <c r="B47" s="198" t="s">
+      <c r="B47" s="70" t="s">
         <v>134</v>
       </c>
       <c r="C47" s="30"/>
-      <c r="D47" s="199">
-        <v>10000</v>
-      </c>
-      <c r="E47" s="200" t="str">
+      <c r="D47" s="148">
+        <v>0</v>
+      </c>
+      <c r="E47" s="34" t="str">
         <f>HYPERLINK(اضافات!N47)</f>
-        <v>1559</v>
-      </c>
-      <c r="F47" s="200" t="str">
+        <v>0</v>
+      </c>
+      <c r="F47" s="34" t="str">
         <f>HYPERLINK(اضافات!M47)</f>
         <v>0</v>
       </c>
-      <c r="G47" s="200" t="str">
+      <c r="G47" s="34" t="str">
         <f>HYPERLINK(اضافات!F47)</f>
         <v>0</v>
       </c>
-      <c r="H47" s="200" t="str">
+      <c r="H47" s="34" t="str">
         <f>HYPERLINK(اضافات!O47)</f>
         <v>0</v>
       </c>
-      <c r="I47" s="201" t="str">
+      <c r="I47" s="93" t="str">
         <f>HYPERLINK(خصومات!L47)</f>
-        <v>6333</v>
-      </c>
-      <c r="J47" s="202">
+        <v>0</v>
+      </c>
+      <c r="J47" s="163">
         <f t="shared" si="0"/>
-        <v>11559</v>
-      </c>
-      <c r="K47" s="202">
+        <v>0</v>
+      </c>
+      <c r="K47" s="163">
         <f t="shared" si="1"/>
-        <v>3667</v>
+        <v>0</v>
       </c>
       <c r="L47" s="32"/>
       <c r="M47" s="28"/>
@@ -4747,12 +4641,12 @@
         <v>135</v>
       </c>
       <c r="C48" s="30"/>
-      <c r="D48" s="151">
-        <v>12000</v>
+      <c r="D48" s="148">
+        <v>0</v>
       </c>
       <c r="E48" s="34" t="str">
         <f>HYPERLINK(اضافات!N48)</f>
-        <v>1863</v>
+        <v>0</v>
       </c>
       <c r="F48" s="34" t="str">
         <f>HYPERLINK(اضافات!M48)</f>
@@ -4768,15 +4662,15 @@
       </c>
       <c r="I48" s="93" t="str">
         <f>HYPERLINK(خصومات!L48)</f>
-        <v>1750</v>
-      </c>
-      <c r="J48" s="164">
+        <v>0</v>
+      </c>
+      <c r="J48" s="163">
         <f t="shared" si="0"/>
-        <v>13863</v>
-      </c>
-      <c r="K48" s="164">
+        <v>0</v>
+      </c>
+      <c r="K48" s="163">
         <f t="shared" si="1"/>
-        <v>10250</v>
+        <v>0</v>
       </c>
       <c r="L48" s="32"/>
       <c r="M48" s="28"/>
@@ -4789,11 +4683,11 @@
         <v>15</v>
       </c>
       <c r="B49" s="70" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C49" s="30"/>
-      <c r="D49" s="151">
-        <v>8500</v>
+      <c r="D49" s="148">
+        <v>0</v>
       </c>
       <c r="E49" s="34" t="str">
         <f>HYPERLINK(اضافات!N49)</f>
@@ -4815,13 +4709,13 @@
         <f>HYPERLINK(خصومات!L49)</f>
         <v>0</v>
       </c>
-      <c r="J49" s="164">
+      <c r="J49" s="163">
         <f t="shared" si="0"/>
-        <v>8500</v>
-      </c>
-      <c r="K49" s="164">
+        <v>0</v>
+      </c>
+      <c r="K49" s="163">
         <f t="shared" si="1"/>
-        <v>8500</v>
+        <v>0</v>
       </c>
       <c r="L49" s="32"/>
       <c r="M49" s="28"/>
@@ -5097,7 +4991,7 @@
       <c r="C56" s="119"/>
       <c r="D56" s="152">
         <f>SUM(D19:D55)</f>
-        <v>471300</v>
+        <v>0</v>
       </c>
       <c r="E56" s="120">
         <f t="shared" ref="E56:K56" si="3">SUM(E19:E55)</f>
@@ -5121,15 +5015,15 @@
       </c>
       <c r="J56" s="152">
         <f t="shared" si="3"/>
-        <v>579869</v>
+        <v>0</v>
       </c>
       <c r="K56" s="152">
         <f t="shared" si="3"/>
-        <v>456200</v>
+        <v>0</v>
       </c>
       <c r="L56" s="120">
         <f>SUM(K19:K55)</f>
-        <v>456200</v>
+        <v>0</v>
       </c>
       <c r="M56" s="121"/>
       <c r="N56" s="122"/>
@@ -5144,16 +5038,16 @@
         <v>71</v>
       </c>
       <c r="C57" s="25"/>
-      <c r="D57" s="151">
-        <v>128000</v>
+      <c r="D57" s="148">
+        <v>0</v>
       </c>
       <c r="E57" s="34" t="str">
         <f>HYPERLINK(اضافات!N57)</f>
-        <v>44284.75</v>
+        <v>0</v>
       </c>
       <c r="F57" s="34" t="str">
         <f>HYPERLINK(اضافات!M57)</f>
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="G57" s="34" t="str">
         <f>HYPERLINK(اضافات!F57)</f>
@@ -5165,15 +5059,15 @@
       </c>
       <c r="I57" s="93" t="str">
         <f>HYPERLINK(خصومات!L57)</f>
-        <v>10000</v>
-      </c>
-      <c r="J57" s="164">
+        <v>0</v>
+      </c>
+      <c r="J57" s="163">
         <f t="shared" si="0"/>
-        <v>174884.75</v>
-      </c>
-      <c r="K57" s="164">
+        <v>0</v>
+      </c>
+      <c r="K57" s="163">
         <f t="shared" si="1"/>
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="L57" s="26"/>
       <c r="M57" s="28"/>
@@ -5189,16 +5083,16 @@
         <v>132</v>
       </c>
       <c r="C58" s="25"/>
-      <c r="D58" s="151">
-        <v>45000</v>
+      <c r="D58" s="148">
+        <v>0</v>
       </c>
       <c r="E58" s="34" t="str">
         <f>HYPERLINK(اضافات!N58)</f>
-        <v>14363.75</v>
+        <v>0</v>
       </c>
       <c r="F58" s="34" t="str">
         <f>HYPERLINK(اضافات!M58)</f>
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="G58" s="34" t="str">
         <f>HYPERLINK(اضافات!F58)</f>
@@ -5212,13 +5106,13 @@
         <f>HYPERLINK(خصومات!L58)</f>
         <v>0</v>
       </c>
-      <c r="J58" s="164">
+      <c r="J58" s="163">
         <f t="shared" si="0"/>
-        <v>61663.75</v>
-      </c>
-      <c r="K58" s="164">
+        <v>0</v>
+      </c>
+      <c r="K58" s="163">
         <f t="shared" si="1"/>
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="L58" s="26"/>
       <c r="M58" s="28"/>
@@ -5232,7 +5126,7 @@
         <v>95</v>
       </c>
       <c r="C59" s="25"/>
-      <c r="D59" s="151">
+      <c r="D59" s="148">
         <v>0</v>
       </c>
       <c r="E59" s="34" t="str">
@@ -5255,11 +5149,11 @@
         <f>HYPERLINK(خصومات!L59)</f>
         <v>0</v>
       </c>
-      <c r="J59" s="164">
+      <c r="J59" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K59" s="164">
+      <c r="K59" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5275,7 +5169,7 @@
         <v>95</v>
       </c>
       <c r="C60" s="25"/>
-      <c r="D60" s="151">
+      <c r="D60" s="148">
         <v>0</v>
       </c>
       <c r="E60" s="34" t="str">
@@ -5298,11 +5192,11 @@
         <f>HYPERLINK(خصومات!L60)</f>
         <v>0</v>
       </c>
-      <c r="J60" s="164">
+      <c r="J60" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K60" s="164">
+      <c r="K60" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5318,7 +5212,7 @@
         <v>95</v>
       </c>
       <c r="C61" s="25"/>
-      <c r="D61" s="151">
+      <c r="D61" s="148">
         <v>0</v>
       </c>
       <c r="E61" s="34" t="str">
@@ -5341,11 +5235,11 @@
         <f>HYPERLINK(خصومات!L61)</f>
         <v>0</v>
       </c>
-      <c r="J61" s="164">
+      <c r="J61" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K61" s="164">
+      <c r="K61" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5363,16 +5257,16 @@
         <v>70</v>
       </c>
       <c r="C62" s="3"/>
-      <c r="D62" s="151">
-        <v>38000</v>
+      <c r="D62" s="148">
+        <v>0</v>
       </c>
       <c r="E62" s="85" t="str">
         <f>HYPERLINK(اضافات!N62)</f>
-        <v>12522.75</v>
+        <v>0</v>
       </c>
       <c r="F62" s="85" t="str">
         <f>HYPERLINK(اضافات!M62)</f>
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="G62" s="85" t="str">
         <f>HYPERLINK(اضافات!F62)</f>
@@ -5384,15 +5278,15 @@
       </c>
       <c r="I62" s="93" t="str">
         <f>HYPERLINK(خصومات!L62)</f>
-        <v>634.5</v>
-      </c>
-      <c r="J62" s="164">
+        <v>0</v>
+      </c>
+      <c r="J62" s="163">
         <f t="shared" si="0"/>
-        <v>52722.75</v>
-      </c>
-      <c r="K62" s="164">
+        <v>0</v>
+      </c>
+      <c r="K62" s="163">
         <f t="shared" si="1"/>
-        <v>37365.5</v>
+        <v>0</v>
       </c>
       <c r="L62" s="86"/>
       <c r="M62" s="10"/>
@@ -5408,16 +5302,16 @@
         <v>75</v>
       </c>
       <c r="C63" s="25"/>
-      <c r="D63" s="151">
-        <v>30000</v>
+      <c r="D63" s="148">
+        <v>0</v>
       </c>
       <c r="E63" s="34" t="str">
         <f>HYPERLINK(اضافات!N63)</f>
-        <v>10860.75</v>
+        <v>0</v>
       </c>
       <c r="F63" s="34" t="str">
         <f>HYPERLINK(اضافات!M63)</f>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="G63" s="34" t="str">
         <f>HYPERLINK(اضافات!F63)</f>
@@ -5431,13 +5325,13 @@
         <f>HYPERLINK(خصومات!L63)</f>
         <v>0</v>
       </c>
-      <c r="J63" s="164">
+      <c r="J63" s="163">
         <f t="shared" si="0"/>
-        <v>42860.75</v>
-      </c>
-      <c r="K63" s="164">
+        <v>0</v>
+      </c>
+      <c r="K63" s="163">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="L63" s="26"/>
       <c r="M63" s="28"/>
@@ -5451,7 +5345,7 @@
         <v>94</v>
       </c>
       <c r="C64" s="25"/>
-      <c r="D64" s="151">
+      <c r="D64" s="148">
         <v>0</v>
       </c>
       <c r="E64" s="34" t="str">
@@ -5474,11 +5368,11 @@
         <f>HYPERLINK(خصومات!L64)</f>
         <v>0</v>
       </c>
-      <c r="J64" s="164">
+      <c r="J64" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K64" s="164">
+      <c r="K64" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5494,7 +5388,7 @@
         <v>94</v>
       </c>
       <c r="C65" s="25"/>
-      <c r="D65" s="151">
+      <c r="D65" s="148">
         <v>0</v>
       </c>
       <c r="E65" s="34" t="str">
@@ -5517,11 +5411,11 @@
         <f>HYPERLINK(خصومات!L65)</f>
         <v>0</v>
       </c>
-      <c r="J65" s="164">
+      <c r="J65" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K65" s="164">
+      <c r="K65" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5537,7 +5431,7 @@
         <v>94</v>
       </c>
       <c r="C66" s="25"/>
-      <c r="D66" s="151">
+      <c r="D66" s="148">
         <v>0</v>
       </c>
       <c r="E66" s="34" t="str">
@@ -5560,11 +5454,11 @@
         <f>HYPERLINK(خصومات!L66)</f>
         <v>0</v>
       </c>
-      <c r="J66" s="164">
+      <c r="J66" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K66" s="164">
+      <c r="K66" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5580,7 +5474,7 @@
         <v>94</v>
       </c>
       <c r="C67" s="25"/>
-      <c r="D67" s="151">
+      <c r="D67" s="148">
         <v>0</v>
       </c>
       <c r="E67" s="34" t="str">
@@ -5603,11 +5497,11 @@
         <f>HYPERLINK(خصومات!L67)</f>
         <v>0</v>
       </c>
-      <c r="J67" s="164">
+      <c r="J67" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K67" s="164">
+      <c r="K67" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5625,16 +5519,16 @@
         <v>137</v>
       </c>
       <c r="C68" s="25"/>
-      <c r="D68" s="151">
-        <v>40000</v>
+      <c r="D68" s="148">
+        <v>0</v>
       </c>
       <c r="E68" s="34" t="str">
         <f>HYPERLINK(اضافات!N68)</f>
-        <v>13460.75</v>
+        <v>0</v>
       </c>
       <c r="F68" s="34" t="str">
         <f>HYPERLINK(اضافات!M68)</f>
-        <v>2405</v>
+        <v>0</v>
       </c>
       <c r="G68" s="34" t="str">
         <f>HYPERLINK(اضافات!F68)</f>
@@ -5648,13 +5542,13 @@
         <f>HYPERLINK(خصومات!L68)</f>
         <v>0</v>
       </c>
-      <c r="J68" s="164">
+      <c r="J68" s="163">
         <f t="shared" si="0"/>
-        <v>55865.75</v>
-      </c>
-      <c r="K68" s="164">
+        <v>0</v>
+      </c>
+      <c r="K68" s="163">
         <f t="shared" si="1"/>
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="L68" s="26"/>
       <c r="M68" s="28"/>
@@ -5670,16 +5564,16 @@
         <v>131</v>
       </c>
       <c r="C69" s="25"/>
-      <c r="D69" s="151">
-        <v>18000</v>
+      <c r="D69" s="148">
+        <v>0</v>
       </c>
       <c r="E69" s="34" t="str">
         <f>HYPERLINK(اضافات!N69)</f>
-        <v>7871.89</v>
+        <v>0</v>
       </c>
       <c r="F69" s="34" t="str">
         <f>HYPERLINK(اضافات!M69)</f>
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="G69" s="34" t="str">
         <f>HYPERLINK(اضافات!F69)</f>
@@ -5693,13 +5587,13 @@
         <f>HYPERLINK(خصومات!L69)</f>
         <v>0</v>
       </c>
-      <c r="J69" s="164">
+      <c r="J69" s="163">
         <f t="shared" ref="J69:J117" si="4">SUM(D69,VALUE(E69),VALUE(F69),VALUE(G69))</f>
-        <v>27971.89</v>
-      </c>
-      <c r="K69" s="164">
+        <v>0</v>
+      </c>
+      <c r="K69" s="163">
         <f t="shared" ref="K69:K100" si="5">VALUE(D69)+VALUE(G69)+VALUE(H69)-VALUE(I69)</f>
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="L69" s="26"/>
       <c r="M69" s="28"/>
@@ -5708,48 +5602,48 @@
       <c r="P69" s="27"/>
     </row>
     <row r="70" spans="1:16" s="51" customFormat="1" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="A70" s="186">
-        <v>0</v>
-      </c>
-      <c r="B70" s="187" t="s">
+      <c r="A70" s="31">
+        <v>0</v>
+      </c>
+      <c r="B70" s="70" t="s">
         <v>96</v>
       </c>
       <c r="C70" s="25"/>
-      <c r="D70" s="188">
-        <v>0</v>
-      </c>
-      <c r="E70" s="189" t="str">
+      <c r="D70" s="148">
+        <v>0</v>
+      </c>
+      <c r="E70" s="34" t="str">
         <f>HYPERLINK(اضافات!N70)</f>
-        <v>3433.01</v>
-      </c>
-      <c r="F70" s="189" t="str">
+        <v>0</v>
+      </c>
+      <c r="F70" s="34" t="str">
         <f>HYPERLINK(اضافات!M70)</f>
         <v>0</v>
       </c>
-      <c r="G70" s="189" t="str">
+      <c r="G70" s="34" t="str">
         <f>HYPERLINK(اضافات!F70)</f>
         <v>0</v>
       </c>
-      <c r="H70" s="189" t="str">
+      <c r="H70" s="34" t="str">
         <f>HYPERLINK(اضافات!O70)</f>
         <v>0</v>
       </c>
-      <c r="I70" s="190" t="str">
+      <c r="I70" s="93" t="str">
         <f>HYPERLINK(خصومات!L70)</f>
         <v>0</v>
       </c>
-      <c r="J70" s="191">
+      <c r="J70" s="163">
         <f t="shared" si="4"/>
-        <v>3433.01</v>
-      </c>
-      <c r="K70" s="191">
+        <v>0</v>
+      </c>
+      <c r="K70" s="163">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L70" s="26"/>
-      <c r="M70" s="192"/>
+      <c r="M70" s="171"/>
       <c r="N70" s="57"/>
-      <c r="O70" s="180"/>
+      <c r="O70" s="169"/>
       <c r="P70" s="27"/>
     </row>
     <row r="71" spans="1:16" s="51" customFormat="1" ht="16.8" x14ac:dyDescent="0.25">
@@ -5760,16 +5654,16 @@
         <v>138</v>
       </c>
       <c r="C71" s="25"/>
-      <c r="D71" s="151">
-        <v>22000</v>
+      <c r="D71" s="148">
+        <v>0</v>
       </c>
       <c r="E71" s="34" t="str">
         <f>HYPERLINK(اضافات!N71)</f>
-        <v>5056</v>
+        <v>0</v>
       </c>
       <c r="F71" s="34" t="str">
         <f>HYPERLINK(اضافات!M71)</f>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="G71" s="34" t="str">
         <f>HYPERLINK(اضافات!F71)</f>
@@ -5783,13 +5677,13 @@
         <f>HYPERLINK(خصومات!L71)</f>
         <v>0</v>
       </c>
-      <c r="J71" s="164">
+      <c r="J71" s="163">
         <f t="shared" si="4"/>
-        <v>29056</v>
-      </c>
-      <c r="K71" s="164">
+        <v>0</v>
+      </c>
+      <c r="K71" s="163">
         <f t="shared" si="5"/>
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="L71" s="26"/>
       <c r="M71" s="28"/>
@@ -5805,16 +5699,16 @@
         <v>74</v>
       </c>
       <c r="C72" s="25"/>
-      <c r="D72" s="151">
-        <v>22000</v>
+      <c r="D72" s="148">
+        <v>0</v>
       </c>
       <c r="E72" s="34" t="str">
         <f>HYPERLINK(اضافات!N72)</f>
-        <v>9013.75</v>
+        <v>0</v>
       </c>
       <c r="F72" s="34" t="str">
         <f>HYPERLINK(اضافات!M72)</f>
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="G72" s="34" t="str">
         <f>HYPERLINK(اضافات!F72)</f>
@@ -5826,15 +5720,15 @@
       </c>
       <c r="I72" s="93" t="str">
         <f>HYPERLINK(خصومات!L72)</f>
-        <v>1286</v>
-      </c>
-      <c r="J72" s="164">
+        <v>0</v>
+      </c>
+      <c r="J72" s="163">
         <f t="shared" si="4"/>
-        <v>33113.75</v>
-      </c>
-      <c r="K72" s="164">
+        <v>0</v>
+      </c>
+      <c r="K72" s="163">
         <f t="shared" si="5"/>
-        <v>20714</v>
+        <v>0</v>
       </c>
       <c r="L72" s="26"/>
       <c r="M72" s="28"/>
@@ -5850,16 +5744,16 @@
         <v>125</v>
       </c>
       <c r="C73" s="25"/>
-      <c r="D73" s="151">
-        <v>15000</v>
+      <c r="D73" s="148">
+        <v>0</v>
       </c>
       <c r="E73" s="34" t="str">
         <f>HYPERLINK(اضافات!N73)</f>
-        <v>5930.15</v>
+        <v>0</v>
       </c>
       <c r="F73" s="34" t="str">
         <f>HYPERLINK(اضافات!M73)</f>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="G73" s="34" t="str">
         <f>HYPERLINK(اضافات!F73)</f>
@@ -5873,13 +5767,13 @@
         <f>HYPERLINK(خصومات!L73)</f>
         <v>0</v>
       </c>
-      <c r="J73" s="164">
+      <c r="J73" s="163">
         <f t="shared" si="4"/>
-        <v>22930.15</v>
-      </c>
-      <c r="K73" s="164">
+        <v>0</v>
+      </c>
+      <c r="K73" s="163">
         <f t="shared" si="5"/>
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="L73" s="26"/>
       <c r="M73" s="28"/>
@@ -5895,16 +5789,16 @@
         <v>73</v>
       </c>
       <c r="C74" s="25"/>
-      <c r="D74" s="151">
-        <v>15000</v>
+      <c r="D74" s="148">
+        <v>0</v>
       </c>
       <c r="E74" s="34" t="str">
         <f>HYPERLINK(اضافات!N74)</f>
-        <v>6223.15</v>
+        <v>0</v>
       </c>
       <c r="F74" s="34" t="str">
         <f>HYPERLINK(اضافات!M74)</f>
-        <v>2415</v>
+        <v>0</v>
       </c>
       <c r="G74" s="34" t="str">
         <f>HYPERLINK(اضافات!F74)</f>
@@ -5918,13 +5812,13 @@
         <f>HYPERLINK(خصومات!L74)</f>
         <v>0</v>
       </c>
-      <c r="J74" s="164">
+      <c r="J74" s="163">
         <f t="shared" si="4"/>
-        <v>23638.15</v>
-      </c>
-      <c r="K74" s="164">
+        <v>0</v>
+      </c>
+      <c r="K74" s="163">
         <f t="shared" si="5"/>
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="L74" s="26"/>
       <c r="M74" s="28"/>
@@ -5940,16 +5834,16 @@
         <v>144</v>
       </c>
       <c r="C75" s="25"/>
-      <c r="D75" s="151">
-        <v>14000</v>
+      <c r="D75" s="148">
+        <v>0</v>
       </c>
       <c r="E75" s="34" t="str">
         <f>HYPERLINK(اضافات!N75)</f>
-        <v>5852</v>
+        <v>0</v>
       </c>
       <c r="F75" s="34" t="str">
         <f>HYPERLINK(اضافات!M75)</f>
-        <v>2315</v>
+        <v>0</v>
       </c>
       <c r="G75" s="34" t="str">
         <f>HYPERLINK(اضافات!F75)</f>
@@ -5963,13 +5857,13 @@
         <f>HYPERLINK(خصومات!L75)</f>
         <v>0</v>
       </c>
-      <c r="J75" s="164">
+      <c r="J75" s="163">
         <f t="shared" si="4"/>
-        <v>22167</v>
-      </c>
-      <c r="K75" s="164">
+        <v>0</v>
+      </c>
+      <c r="K75" s="163">
         <f t="shared" si="5"/>
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="L75" s="26"/>
       <c r="M75" s="28"/>
@@ -5985,16 +5879,16 @@
         <v>139</v>
       </c>
       <c r="C76" s="25"/>
-      <c r="D76" s="151">
-        <v>13500</v>
+      <c r="D76" s="148">
+        <v>0</v>
       </c>
       <c r="E76" s="34" t="str">
         <f>HYPERLINK(اضافات!N76)</f>
-        <v>5618</v>
+        <v>0</v>
       </c>
       <c r="F76" s="34" t="str">
         <f>HYPERLINK(اضافات!M76)</f>
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="G76" s="34" t="str">
         <f>HYPERLINK(اضافات!F76)</f>
@@ -6008,13 +5902,13 @@
         <f>HYPERLINK(خصومات!L76)</f>
         <v>0</v>
       </c>
-      <c r="J76" s="164">
+      <c r="J76" s="163">
         <f t="shared" si="4"/>
-        <v>21618</v>
-      </c>
-      <c r="K76" s="164">
+        <v>0</v>
+      </c>
+      <c r="K76" s="163">
         <f t="shared" si="5"/>
-        <v>13500</v>
+        <v>0</v>
       </c>
       <c r="L76" s="26"/>
       <c r="M76" s="28"/>
@@ -6030,16 +5924,16 @@
         <v>140</v>
       </c>
       <c r="C77" s="25"/>
-      <c r="D77" s="151">
-        <v>12000</v>
+      <c r="D77" s="148">
+        <v>0</v>
       </c>
       <c r="E77" s="34" t="str">
         <f>HYPERLINK(اضافات!N77)</f>
-        <v>4772</v>
+        <v>0</v>
       </c>
       <c r="F77" s="34" t="str">
         <f>HYPERLINK(اضافات!M77)</f>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="G77" s="34" t="str">
         <f>HYPERLINK(اضافات!F77)</f>
@@ -6053,13 +5947,13 @@
         <f>HYPERLINK(خصومات!L77)</f>
         <v>0</v>
       </c>
-      <c r="J77" s="164">
+      <c r="J77" s="163">
         <f t="shared" si="4"/>
-        <v>18772</v>
-      </c>
-      <c r="K77" s="164">
+        <v>0</v>
+      </c>
+      <c r="K77" s="163">
         <f t="shared" si="5"/>
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="L77" s="26"/>
       <c r="M77" s="28"/>
@@ -6075,16 +5969,16 @@
         <v>141</v>
       </c>
       <c r="C78" s="25"/>
-      <c r="D78" s="151">
-        <v>11000</v>
+      <c r="D78" s="148">
+        <v>0</v>
       </c>
       <c r="E78" s="34" t="str">
         <f>HYPERLINK(اضافات!N78)</f>
-        <v>4893</v>
+        <v>0</v>
       </c>
       <c r="F78" s="34" t="str">
         <f>HYPERLINK(اضافات!M78)</f>
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="G78" s="34" t="str">
         <f>HYPERLINK(اضافات!F78)</f>
@@ -6098,13 +5992,13 @@
         <f>HYPERLINK(خصومات!L78)</f>
         <v>0</v>
       </c>
-      <c r="J78" s="164">
+      <c r="J78" s="163">
         <f t="shared" si="4"/>
-        <v>18193</v>
-      </c>
-      <c r="K78" s="164">
+        <v>0</v>
+      </c>
+      <c r="K78" s="163">
         <f t="shared" si="5"/>
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="L78" s="26"/>
       <c r="M78" s="28"/>
@@ -6120,16 +6014,16 @@
         <v>76</v>
       </c>
       <c r="C79" s="25"/>
-      <c r="D79" s="151">
-        <v>11000</v>
+      <c r="D79" s="148">
+        <v>0</v>
       </c>
       <c r="E79" s="34" t="str">
         <f>HYPERLINK(اضافات!N79)</f>
-        <v>4288</v>
+        <v>0</v>
       </c>
       <c r="F79" s="34" t="str">
         <f>HYPERLINK(اضافات!M79)</f>
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="G79" s="34" t="str">
         <f>HYPERLINK(اضافات!F79)</f>
@@ -6143,13 +6037,13 @@
         <f>HYPERLINK(خصومات!L79)</f>
         <v>0</v>
       </c>
-      <c r="J79" s="164">
+      <c r="J79" s="163">
         <f t="shared" si="4"/>
-        <v>17488</v>
-      </c>
-      <c r="K79" s="164">
+        <v>0</v>
+      </c>
+      <c r="K79" s="163">
         <f t="shared" si="5"/>
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="L79" s="26"/>
       <c r="M79" s="28"/>
@@ -6163,7 +6057,7 @@
       </c>
       <c r="B80" s="70"/>
       <c r="C80" s="25"/>
-      <c r="D80" s="151">
+      <c r="D80" s="148">
         <v>0</v>
       </c>
       <c r="E80" s="34" t="str">
@@ -6186,18 +6080,16 @@
         <f>HYPERLINK(خصومات!L80)</f>
         <v>0</v>
       </c>
-      <c r="J80" s="164">
+      <c r="J80" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K80" s="164">
+      <c r="K80" s="163">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L80" s="26"/>
-      <c r="M80" s="28" t="s">
-        <v>146</v>
-      </c>
+      <c r="M80" s="28"/>
       <c r="N80" s="57"/>
       <c r="O80" s="56"/>
       <c r="P80" s="27"/>
@@ -6210,16 +6102,16 @@
         <v>142</v>
       </c>
       <c r="C81" s="25"/>
-      <c r="D81" s="151">
-        <v>16000</v>
+      <c r="D81" s="148">
+        <v>0</v>
       </c>
       <c r="E81" s="34" t="str">
         <f>HYPERLINK(اضافات!N81)</f>
-        <v>6857</v>
+        <v>0</v>
       </c>
       <c r="F81" s="34" t="str">
         <f>HYPERLINK(اضافات!M81)</f>
-        <v>2550</v>
+        <v>0</v>
       </c>
       <c r="G81" s="34" t="str">
         <f>HYPERLINK(اضافات!F81)</f>
@@ -6233,13 +6125,13 @@
         <f>HYPERLINK(خصومات!L81)</f>
         <v>0</v>
       </c>
-      <c r="J81" s="164">
+      <c r="J81" s="163">
         <f t="shared" si="4"/>
-        <v>25407</v>
-      </c>
-      <c r="K81" s="164">
+        <v>0</v>
+      </c>
+      <c r="K81" s="163">
         <f t="shared" si="5"/>
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="L81" s="26"/>
       <c r="M81" s="28"/>
@@ -6255,16 +6147,16 @@
         <v>126</v>
       </c>
       <c r="C82" s="25"/>
-      <c r="D82" s="151">
-        <v>10000</v>
+      <c r="D82" s="148">
+        <v>0</v>
       </c>
       <c r="E82" s="34" t="str">
         <f>HYPERLINK(اضافات!N82)</f>
-        <v>3711</v>
+        <v>0</v>
       </c>
       <c r="F82" s="34" t="str">
         <f>HYPERLINK(اضافات!M82)</f>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="G82" s="34" t="str">
         <f>HYPERLINK(اضافات!F82)</f>
@@ -6278,13 +6170,13 @@
         <f>HYPERLINK(خصومات!L82)</f>
         <v>0</v>
       </c>
-      <c r="J82" s="164">
+      <c r="J82" s="163">
         <f t="shared" si="4"/>
-        <v>15711</v>
-      </c>
-      <c r="K82" s="164">
+        <v>0</v>
+      </c>
+      <c r="K82" s="163">
         <f t="shared" si="5"/>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="L82" s="26"/>
       <c r="M82" s="28"/>
@@ -6300,16 +6192,16 @@
         <v>143</v>
       </c>
       <c r="C83" s="25"/>
-      <c r="D83" s="166">
-        <v>9000</v>
+      <c r="D83" s="148">
+        <v>0</v>
       </c>
       <c r="E83" s="34" t="str">
         <f>HYPERLINK(اضافات!N83)</f>
-        <v>2286</v>
+        <v>0</v>
       </c>
       <c r="F83" s="34" t="str">
         <f>HYPERLINK(اضافات!M83)</f>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="G83" s="34" t="str">
         <f>HYPERLINK(اضافات!F83)</f>
@@ -6323,56 +6215,56 @@
         <f>HYPERLINK(خصومات!L83)</f>
         <v>0</v>
       </c>
-      <c r="J83" s="164">
+      <c r="J83" s="163">
         <f t="shared" si="4"/>
-        <v>13286</v>
-      </c>
-      <c r="K83" s="164">
+        <v>0</v>
+      </c>
+      <c r="K83" s="163">
         <f t="shared" si="5"/>
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="L83" s="26"/>
       <c r="M83" s="28"/>
       <c r="N83" s="57"/>
-      <c r="O83" s="180"/>
+      <c r="O83" s="169"/>
       <c r="P83" s="27"/>
     </row>
     <row r="84" spans="1:16" s="55" customFormat="1" ht="16.8" x14ac:dyDescent="0.25">
-      <c r="A84" s="169">
+      <c r="A84" s="31">
         <v>19</v>
       </c>
-      <c r="B84" s="170" t="s">
-        <v>148</v>
-      </c>
-      <c r="C84" s="171"/>
-      <c r="D84" s="172">
-        <v>3700</v>
-      </c>
-      <c r="E84" s="173" t="str">
+      <c r="B84" s="70" t="s">
+        <v>146</v>
+      </c>
+      <c r="C84" s="25"/>
+      <c r="D84" s="148">
+        <v>0</v>
+      </c>
+      <c r="E84" s="34" t="str">
         <f>HYPERLINK(اضافات!N84)</f>
-        <v>1102</v>
-      </c>
-      <c r="F84" s="173" t="str">
+        <v>0</v>
+      </c>
+      <c r="F84" s="34" t="str">
         <f>HYPERLINK(اضافات!M84)</f>
         <v>0</v>
       </c>
-      <c r="G84" s="173" t="str">
+      <c r="G84" s="34" t="str">
         <f>HYPERLINK(اضافات!F84)</f>
         <v>0</v>
       </c>
-      <c r="H84" s="173" t="str">
+      <c r="H84" s="34" t="str">
         <f>HYPERLINK(اضافات!O84)</f>
         <v>0</v>
       </c>
-      <c r="I84" s="174" t="str">
+      <c r="I84" s="93" t="str">
         <f>HYPERLINK(خصومات!L84)</f>
-        <v>3700</v>
-      </c>
-      <c r="J84" s="175">
+        <v>0</v>
+      </c>
+      <c r="J84" s="163">
         <f t="shared" si="4"/>
-        <v>4802</v>
-      </c>
-      <c r="K84" s="176">
+        <v>0</v>
+      </c>
+      <c r="K84" s="163">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6382,24 +6274,24 @@
       <c r="O84" s="56"/>
       <c r="P84" s="27"/>
     </row>
-    <row r="85" spans="1:16" s="55" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" s="55" customFormat="1" ht="16.8" x14ac:dyDescent="0.25">
       <c r="A85" s="31">
         <v>20</v>
       </c>
-      <c r="B85" s="82" t="s">
-        <v>163</v>
+      <c r="B85" s="70" t="s">
+        <v>154</v>
       </c>
       <c r="C85" s="25"/>
-      <c r="D85" s="151">
-        <v>13000</v>
+      <c r="D85" s="148">
+        <v>0</v>
       </c>
       <c r="E85" s="34" t="str">
         <f>HYPERLINK(اضافات!N85)</f>
-        <v>5171.5</v>
+        <v>0</v>
       </c>
       <c r="F85" s="34" t="str">
         <f>HYPERLINK(اضافات!M85)</f>
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="G85" s="34" t="str">
         <f>HYPERLINK(اضافات!F85)</f>
@@ -6411,21 +6303,21 @@
       </c>
       <c r="I85" s="93" t="str">
         <f>HYPERLINK(خصومات!L85)</f>
-        <v>9100</v>
-      </c>
-      <c r="J85" s="164">
+        <v>0</v>
+      </c>
+      <c r="J85" s="163">
         <f t="shared" si="4"/>
-        <v>20271.5</v>
-      </c>
-      <c r="K85" s="164">
+        <v>0</v>
+      </c>
+      <c r="K85" s="163">
         <f t="shared" si="5"/>
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="L85" s="26"/>
       <c r="M85" s="28"/>
       <c r="N85" s="57"/>
-      <c r="O85" s="180" t="s">
-        <v>167</v>
+      <c r="O85" s="169" t="s">
+        <v>157</v>
       </c>
       <c r="P85" s="27"/>
     </row>
@@ -7084,7 +6976,7 @@
       <c r="C101" s="119"/>
       <c r="D101" s="152">
         <f>SUM(D57:D100)</f>
-        <v>486200</v>
+        <v>0</v>
       </c>
       <c r="E101" s="120">
         <f t="shared" ref="E101:K101" si="6">SUM(E57:E100)</f>
@@ -7108,15 +7000,15 @@
       </c>
       <c r="J101" s="149">
         <f t="shared" si="6"/>
-        <v>705856.20000000007</v>
+        <v>0</v>
       </c>
       <c r="K101" s="149">
         <f t="shared" si="6"/>
-        <v>461479.5</v>
+        <v>0</v>
       </c>
       <c r="L101" s="120">
         <f>SUM(K57:K100)</f>
-        <v>461479.5</v>
+        <v>0</v>
       </c>
       <c r="M101" s="126"/>
       <c r="N101" s="126"/>
@@ -7131,8 +7023,8 @@
         <v>85</v>
       </c>
       <c r="C102" s="25"/>
-      <c r="D102" s="151">
-        <v>45000</v>
+      <c r="D102" s="148">
+        <v>0</v>
       </c>
       <c r="E102" s="34" t="str">
         <f>HYPERLINK(اضافات!N102)</f>
@@ -7154,18 +7046,16 @@
         <f>HYPERLINK(خصومات!L102)</f>
         <v>0</v>
       </c>
-      <c r="J102" s="164">
+      <c r="J102" s="163">
         <f t="shared" si="4"/>
-        <v>45000</v>
-      </c>
-      <c r="K102" s="164">
+        <v>0</v>
+      </c>
+      <c r="K102" s="163">
         <f t="shared" ref="K102:K117" si="7">VALUE(D102)+VALUE(G102)+VALUE(H102)-VALUE(I102)</f>
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="L102" s="26"/>
-      <c r="M102" s="28" t="s">
-        <v>146</v>
-      </c>
+      <c r="M102" s="28"/>
       <c r="N102" s="57"/>
       <c r="O102" s="56"/>
       <c r="P102" s="27"/>
@@ -7178,8 +7068,8 @@
         <v>86</v>
       </c>
       <c r="C103" s="25"/>
-      <c r="D103" s="151">
-        <v>30000</v>
+      <c r="D103" s="148">
+        <v>0</v>
       </c>
       <c r="E103" s="34" t="str">
         <f>HYPERLINK(اضافات!N103)</f>
@@ -7201,18 +7091,16 @@
         <f>HYPERLINK(خصومات!L103)</f>
         <v>0</v>
       </c>
-      <c r="J103" s="164">
+      <c r="J103" s="163">
         <f t="shared" si="4"/>
-        <v>30000</v>
-      </c>
-      <c r="K103" s="164">
+        <v>0</v>
+      </c>
+      <c r="K103" s="163">
         <f t="shared" si="7"/>
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="L103" s="26"/>
-      <c r="M103" s="28" t="s">
-        <v>146</v>
-      </c>
+      <c r="M103" s="28"/>
       <c r="N103" s="57"/>
       <c r="O103" s="56"/>
       <c r="P103" s="27"/>
@@ -7225,8 +7113,8 @@
         <v>87</v>
       </c>
       <c r="C104" s="25"/>
-      <c r="D104" s="151">
-        <v>35000</v>
+      <c r="D104" s="148">
+        <v>0</v>
       </c>
       <c r="E104" s="34" t="str">
         <f>HYPERLINK(اضافات!N104)</f>
@@ -7248,18 +7136,16 @@
         <f>HYPERLINK(خصومات!L104)</f>
         <v>0</v>
       </c>
-      <c r="J104" s="164">
+      <c r="J104" s="163">
         <f t="shared" si="4"/>
-        <v>35000</v>
-      </c>
-      <c r="K104" s="164">
+        <v>0</v>
+      </c>
+      <c r="K104" s="163">
         <f t="shared" si="7"/>
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="L104" s="26"/>
-      <c r="M104" s="28" t="s">
-        <v>146</v>
-      </c>
+      <c r="M104" s="28"/>
       <c r="N104" s="57"/>
       <c r="O104" s="56"/>
       <c r="P104" s="27"/>
@@ -7272,12 +7158,12 @@
         <v>88</v>
       </c>
       <c r="C105" s="25"/>
-      <c r="D105" s="151">
-        <v>20000</v>
+      <c r="D105" s="148">
+        <v>0</v>
       </c>
       <c r="E105" s="34" t="str">
         <f>HYPERLINK(اضافات!N105)</f>
-        <v>3045</v>
+        <v>0</v>
       </c>
       <c r="F105" s="34" t="str">
         <f>HYPERLINK(اضافات!M105)</f>
@@ -7295,18 +7181,16 @@
         <f>HYPERLINK(خصومات!L105)</f>
         <v>0</v>
       </c>
-      <c r="J105" s="164">
+      <c r="J105" s="163">
         <f t="shared" si="4"/>
-        <v>23045</v>
-      </c>
-      <c r="K105" s="164">
+        <v>0</v>
+      </c>
+      <c r="K105" s="163">
         <f t="shared" si="7"/>
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="L105" s="26"/>
-      <c r="M105" s="28" t="s">
-        <v>147</v>
-      </c>
+      <c r="M105" s="28"/>
       <c r="N105" s="57"/>
       <c r="O105" s="56"/>
       <c r="P105" s="27"/>
@@ -7318,9 +7202,9 @@
       <c r="B106" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="C106" s="163"/>
-      <c r="D106" s="166">
-        <v>32000</v>
+      <c r="C106" s="25"/>
+      <c r="D106" s="148">
+        <v>0</v>
       </c>
       <c r="E106" s="34" t="str">
         <f>HYPERLINK(اضافات!N106)</f>
@@ -7340,20 +7224,18 @@
       </c>
       <c r="I106" s="93" t="str">
         <f>HYPERLINK(خصومات!L106)</f>
-        <v>1227</v>
-      </c>
-      <c r="J106" s="164">
+        <v>0</v>
+      </c>
+      <c r="J106" s="163">
         <f t="shared" si="4"/>
-        <v>32000</v>
-      </c>
-      <c r="K106" s="164">
+        <v>0</v>
+      </c>
+      <c r="K106" s="163">
         <f t="shared" si="7"/>
-        <v>30773</v>
+        <v>0</v>
       </c>
       <c r="L106" s="26"/>
-      <c r="M106" s="28" t="s">
-        <v>146</v>
-      </c>
+      <c r="M106" s="28"/>
       <c r="N106" s="57"/>
       <c r="O106" s="56"/>
       <c r="P106" s="27"/>
@@ -7366,8 +7248,8 @@
         <v>145</v>
       </c>
       <c r="C107" s="25"/>
-      <c r="D107" s="151">
-        <v>25000</v>
+      <c r="D107" s="148">
+        <v>0</v>
       </c>
       <c r="E107" s="34" t="str">
         <f>HYPERLINK(اضافات!N107)</f>
@@ -7389,18 +7271,16 @@
         <f>HYPERLINK(خصومات!L107)</f>
         <v>0</v>
       </c>
-      <c r="J107" s="164">
+      <c r="J107" s="163">
         <f t="shared" si="4"/>
-        <v>25000</v>
-      </c>
-      <c r="K107" s="164">
+        <v>0</v>
+      </c>
+      <c r="K107" s="163">
         <f t="shared" si="7"/>
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="L107" s="26"/>
-      <c r="M107" s="28" t="s">
-        <v>146</v>
-      </c>
+      <c r="M107" s="28"/>
       <c r="N107" s="57"/>
       <c r="O107" s="56"/>
       <c r="P107" s="27"/>
@@ -7410,10 +7290,10 @@
         <v>7</v>
       </c>
       <c r="B108" s="70" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C108" s="25"/>
-      <c r="D108" s="151">
+      <c r="D108" s="148">
         <v>0</v>
       </c>
       <c r="E108" s="34" t="str">
@@ -7436,11 +7316,11 @@
         <f>HYPERLINK(خصومات!L108)</f>
         <v>0</v>
       </c>
-      <c r="J108" s="164">
+      <c r="J108" s="163">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K108" s="164">
+      <c r="K108" s="163">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -7847,7 +7727,7 @@
       <c r="C118" s="119"/>
       <c r="D118" s="152">
         <f>SUM(D102:D117)</f>
-        <v>187000</v>
+        <v>0</v>
       </c>
       <c r="E118" s="120">
         <f t="shared" ref="E118:K118" si="8">SUM(E102:E117)</f>
@@ -7871,15 +7751,15 @@
       </c>
       <c r="J118" s="152">
         <f t="shared" si="8"/>
-        <v>190045</v>
+        <v>0</v>
       </c>
       <c r="K118" s="152">
         <f t="shared" si="8"/>
-        <v>185773</v>
+        <v>0</v>
       </c>
       <c r="L118" s="120">
         <f>SUM(K102:K117)</f>
-        <v>185773</v>
+        <v>0</v>
       </c>
       <c r="M118" s="126"/>
       <c r="N118" s="126"/>
@@ -7897,7 +7777,7 @@
       <c r="C119" s="74"/>
       <c r="D119" s="153">
         <f>SUM(D18,D56,D101)</f>
-        <v>1577500</v>
+        <v>0</v>
       </c>
       <c r="E119" s="74">
         <f t="shared" ref="E119:J119" si="10">SUM(E18,E56,E101)</f>
@@ -7921,15 +7801,15 @@
       </c>
       <c r="J119" s="153">
         <f t="shared" si="10"/>
-        <v>2104449.2000000002</v>
+        <v>0</v>
       </c>
       <c r="K119" s="153">
         <f>SUM(K18,K56,K101)</f>
-        <v>1537679.5</v>
+        <v>0</v>
       </c>
       <c r="L119" s="74">
         <f>SUM(L18,L56,L101)</f>
-        <v>1537679.5</v>
+        <v>0</v>
       </c>
       <c r="M119" s="74"/>
       <c r="N119" s="13"/>
@@ -7947,7 +7827,7 @@
       <c r="C120" s="74"/>
       <c r="D120" s="154">
         <f t="shared" ref="D120:K120" si="11">SUM(D18,D56,D101,D118)</f>
-        <v>1764500</v>
+        <v>0</v>
       </c>
       <c r="E120" s="76">
         <f t="shared" si="11"/>
@@ -7971,15 +7851,15 @@
       </c>
       <c r="J120" s="154">
         <f t="shared" si="11"/>
-        <v>2294494.2000000002</v>
+        <v>0</v>
       </c>
       <c r="K120" s="154">
         <f t="shared" si="11"/>
-        <v>1723452.5</v>
+        <v>0</v>
       </c>
       <c r="L120" s="76">
         <f>SUM(L18,L56,L101,L118)</f>
-        <v>1723452.5</v>
+        <v>0</v>
       </c>
       <c r="M120" s="74"/>
       <c r="O120" s="21"/>
@@ -8066,17 +7946,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="209" t="s">
+      <c r="A1" s="180" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="210"/>
+      <c r="B1" s="181"/>
     </row>
     <row r="2" spans="1:17" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="135" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="136" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C2" s="137" t="s">
         <v>36</v>
@@ -8179,7 +8059,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="96">
-        <v>1422</v>
+        <v>0</v>
       </c>
       <c r="L4" s="96">
         <v>0</v>
@@ -8190,7 +8070,7 @@
       </c>
       <c r="N4" s="96">
         <f>SUM(I4:K4)</f>
-        <v>1422</v>
+        <v>0</v>
       </c>
       <c r="O4" s="81">
         <f>SUM(G4:H4)</f>
@@ -8198,7 +8078,7 @@
       </c>
       <c r="P4" s="96">
         <f>SUM(M4:O4)</f>
-        <v>1422</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="81"/>
     </row>
@@ -8212,7 +8092,7 @@
         <v>أ/أميرة محمد على شريف</v>
       </c>
       <c r="C5" s="97">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D5" s="97">
         <v>0</v>
@@ -8233,21 +8113,21 @@
         <v>0</v>
       </c>
       <c r="J5" s="97">
-        <v>158904</v>
+        <v>0</v>
       </c>
       <c r="K5" s="97">
-        <v>872</v>
+        <v>0</v>
       </c>
       <c r="L5" s="97">
         <v>0</v>
       </c>
       <c r="M5" s="80">
         <f t="shared" ref="M5:M68" si="0">SUM(C5:E5)+L5</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N5" s="97">
         <f t="shared" ref="N5:N68" si="1">SUM(I5:K5)</f>
-        <v>159776</v>
+        <v>0</v>
       </c>
       <c r="O5" s="80">
         <f t="shared" ref="O5:O68" si="2">SUM(G5:H5)</f>
@@ -8255,7 +8135,7 @@
       </c>
       <c r="P5" s="97">
         <f t="shared" ref="P5:P68" si="3">SUM(M5:O5)</f>
-        <v>160776</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="80"/>
     </row>
@@ -8269,7 +8149,7 @@
         <v>أ/إيهاب حمدى ابراهيم</v>
       </c>
       <c r="C6" s="96">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="D6" s="96">
         <v>0</v>
@@ -8290,21 +8170,21 @@
         <v>0</v>
       </c>
       <c r="J6" s="96">
-        <v>35461</v>
+        <v>0</v>
       </c>
       <c r="K6" s="96">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="L6" s="96">
         <v>0</v>
       </c>
       <c r="M6" s="81">
         <f t="shared" si="0"/>
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="N6" s="96">
         <f t="shared" si="1"/>
-        <v>36051</v>
+        <v>0</v>
       </c>
       <c r="O6" s="81">
         <f t="shared" si="2"/>
@@ -8312,7 +8192,7 @@
       </c>
       <c r="P6" s="96">
         <f t="shared" si="3"/>
-        <v>36526</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="81"/>
     </row>
@@ -8962,9 +8842,9 @@
       <c r="K18" s="146"/>
       <c r="L18" s="146"/>
       <c r="M18" s="146"/>
-      <c r="N18" s="167"/>
+      <c r="N18" s="165"/>
       <c r="O18" s="146"/>
-      <c r="P18" s="167"/>
+      <c r="P18" s="165"/>
       <c r="Q18" s="146"/>
     </row>
     <row r="19" spans="1:17" ht="15" x14ac:dyDescent="0.25">
@@ -8998,10 +8878,10 @@
         <v>0</v>
       </c>
       <c r="J19" s="97">
-        <v>10126</v>
+        <v>0</v>
       </c>
       <c r="K19" s="97">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="L19" s="97">
         <v>0</v>
@@ -9012,7 +8892,7 @@
       </c>
       <c r="N19" s="97">
         <f t="shared" si="1"/>
-        <v>11326</v>
+        <v>0</v>
       </c>
       <c r="O19" s="80">
         <f t="shared" si="2"/>
@@ -9020,7 +8900,7 @@
       </c>
       <c r="P19" s="97">
         <f t="shared" si="3"/>
-        <v>11326</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="80"/>
     </row>
@@ -9034,7 +8914,7 @@
         <v>أ/محمد عبد العزيز عبدالحافظ</v>
       </c>
       <c r="C20" s="96">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="D20" s="96">
         <v>0</v>
@@ -9055,21 +8935,21 @@
         <v>0</v>
       </c>
       <c r="J20" s="96">
-        <v>7116</v>
+        <v>0</v>
       </c>
       <c r="K20" s="96">
-        <v>872</v>
+        <v>0</v>
       </c>
       <c r="L20" s="96">
         <v>0</v>
       </c>
       <c r="M20" s="81">
         <f t="shared" si="0"/>
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="N20" s="96">
         <f t="shared" si="1"/>
-        <v>7988</v>
+        <v>0</v>
       </c>
       <c r="O20" s="81">
         <f t="shared" si="2"/>
@@ -9077,7 +8957,7 @@
       </c>
       <c r="P20" s="96">
         <f t="shared" si="3"/>
-        <v>8463</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="81"/>
     </row>
@@ -9112,10 +8992,10 @@
         <v>0</v>
       </c>
       <c r="J21" s="97">
-        <v>12418</v>
+        <v>0</v>
       </c>
       <c r="K21" s="97">
-        <v>872</v>
+        <v>0</v>
       </c>
       <c r="L21" s="97">
         <v>0</v>
@@ -9126,7 +9006,7 @@
       </c>
       <c r="N21" s="97">
         <f t="shared" si="1"/>
-        <v>13290</v>
+        <v>0</v>
       </c>
       <c r="O21" s="80">
         <f t="shared" si="2"/>
@@ -9134,7 +9014,7 @@
       </c>
       <c r="P21" s="97">
         <f t="shared" si="3"/>
-        <v>13290</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="80"/>
     </row>
@@ -9169,10 +9049,10 @@
         <v>0</v>
       </c>
       <c r="J22" s="96">
-        <v>13860</v>
+        <v>0</v>
       </c>
       <c r="K22" s="96">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="L22" s="96">
         <v>0</v>
@@ -9183,7 +9063,7 @@
       </c>
       <c r="N22" s="96">
         <f t="shared" si="1"/>
-        <v>14450</v>
+        <v>0</v>
       </c>
       <c r="O22" s="81">
         <f t="shared" si="2"/>
@@ -9191,7 +9071,7 @@
       </c>
       <c r="P22" s="96">
         <f t="shared" si="3"/>
-        <v>14450</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="81"/>
     </row>
@@ -9226,10 +9106,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="97">
-        <v>13625</v>
+        <v>0</v>
       </c>
       <c r="K23" s="97">
-        <v>491</v>
+        <v>0</v>
       </c>
       <c r="L23" s="97">
         <v>0</v>
@@ -9240,7 +9120,7 @@
       </c>
       <c r="N23" s="97">
         <f t="shared" si="1"/>
-        <v>14116</v>
+        <v>0</v>
       </c>
       <c r="O23" s="80">
         <f t="shared" si="2"/>
@@ -9248,7 +9128,7 @@
       </c>
       <c r="P23" s="97">
         <f t="shared" si="3"/>
-        <v>14116</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="80"/>
     </row>
@@ -9282,11 +9162,11 @@
       <c r="I24" s="96">
         <v>0</v>
       </c>
-      <c r="J24" s="168">
-        <v>11400</v>
-      </c>
-      <c r="K24" s="168">
-        <v>491</v>
+      <c r="J24" s="166">
+        <v>0</v>
+      </c>
+      <c r="K24" s="166">
+        <v>0</v>
       </c>
       <c r="L24" s="96">
         <v>0</v>
@@ -9297,7 +9177,7 @@
       </c>
       <c r="N24" s="96">
         <f t="shared" si="1"/>
-        <v>11891</v>
+        <v>0</v>
       </c>
       <c r="O24" s="81">
         <f t="shared" si="2"/>
@@ -9305,7 +9185,7 @@
       </c>
       <c r="P24" s="96">
         <f t="shared" si="3"/>
-        <v>11891</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="81"/>
     </row>
@@ -9319,7 +9199,7 @@
         <v>أ/محمد حمدى كامل</v>
       </c>
       <c r="C25" s="97">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="D25" s="97">
         <v>0</v>
@@ -9340,21 +9220,21 @@
         <v>0</v>
       </c>
       <c r="J25" s="97">
-        <v>7355</v>
+        <v>0</v>
       </c>
       <c r="K25" s="97">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="L25" s="97">
         <v>0</v>
       </c>
       <c r="M25" s="80">
         <f t="shared" si="0"/>
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="N25" s="97">
         <f t="shared" si="1"/>
-        <v>7945</v>
+        <v>0</v>
       </c>
       <c r="O25" s="80">
         <f t="shared" si="2"/>
@@ -9362,7 +9242,7 @@
       </c>
       <c r="P25" s="97">
         <f t="shared" si="3"/>
-        <v>8420</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="80"/>
     </row>
@@ -9793,13 +9673,13 @@
         <v>0</v>
       </c>
       <c r="I33" s="97">
-        <v>5250</v>
+        <v>0</v>
       </c>
       <c r="J33" s="97">
-        <v>8177</v>
+        <v>0</v>
       </c>
       <c r="K33" s="97">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="L33" s="97">
         <v>0</v>
@@ -9810,7 +9690,7 @@
       </c>
       <c r="N33" s="97">
         <f t="shared" si="1"/>
-        <v>14100</v>
+        <v>0</v>
       </c>
       <c r="O33" s="80">
         <f t="shared" si="2"/>
@@ -9818,7 +9698,7 @@
       </c>
       <c r="P33" s="97">
         <f t="shared" si="3"/>
-        <v>14100</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="80"/>
     </row>
@@ -9832,7 +9712,7 @@
         <v>أ/هاني أحمد الدالي</v>
       </c>
       <c r="C34" s="96">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="D34" s="96">
         <v>0</v>
@@ -9853,21 +9733,21 @@
         <v>0</v>
       </c>
       <c r="J34" s="96">
-        <v>2234</v>
+        <v>0</v>
       </c>
       <c r="K34" s="96">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="L34" s="96">
         <v>0</v>
       </c>
       <c r="M34" s="81">
         <f t="shared" si="0"/>
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="N34" s="96">
         <f t="shared" si="1"/>
-        <v>2824</v>
+        <v>0</v>
       </c>
       <c r="O34" s="81">
         <f t="shared" si="2"/>
@@ -9875,7 +9755,7 @@
       </c>
       <c r="P34" s="96">
         <f t="shared" si="3"/>
-        <v>3139</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="81"/>
     </row>
@@ -9910,10 +9790,10 @@
         <v>0</v>
       </c>
       <c r="J35" s="97">
-        <v>2027</v>
+        <v>0</v>
       </c>
       <c r="K35" s="97">
-        <v>491</v>
+        <v>0</v>
       </c>
       <c r="L35" s="97">
         <v>0</v>
@@ -9924,7 +9804,7 @@
       </c>
       <c r="N35" s="97">
         <f t="shared" si="1"/>
-        <v>2518</v>
+        <v>0</v>
       </c>
       <c r="O35" s="80">
         <f t="shared" si="2"/>
@@ -9932,7 +9812,7 @@
       </c>
       <c r="P35" s="97">
         <f t="shared" si="3"/>
-        <v>2518</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="80"/>
     </row>
@@ -10474,16 +10354,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="156">
-        <v>5250</v>
+        <v>0</v>
       </c>
       <c r="I45" s="97">
         <v>0</v>
       </c>
       <c r="J45" s="97">
-        <v>1427</v>
+        <v>0</v>
       </c>
       <c r="K45" s="97">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="L45" s="97">
         <v>0</v>
@@ -10494,18 +10374,18 @@
       </c>
       <c r="N45" s="97">
         <f t="shared" si="1"/>
-        <v>1779</v>
+        <v>0</v>
       </c>
       <c r="O45" s="80">
         <f t="shared" si="2"/>
-        <v>5250</v>
+        <v>0</v>
       </c>
       <c r="P45" s="97">
         <f t="shared" si="3"/>
-        <v>7029</v>
-      </c>
-      <c r="Q45" s="197" t="s">
-        <v>154</v>
+        <v>0</v>
+      </c>
+      <c r="Q45" s="176" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="46" spans="1:17" ht="15" x14ac:dyDescent="0.25">
@@ -10539,10 +10419,10 @@
         <v>0</v>
       </c>
       <c r="J46" s="96">
-        <v>1221</v>
+        <v>0</v>
       </c>
       <c r="K46" s="96">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="L46" s="96">
         <v>0</v>
@@ -10553,7 +10433,7 @@
       </c>
       <c r="N46" s="96">
         <f t="shared" si="1"/>
-        <v>1655</v>
+        <v>0</v>
       </c>
       <c r="O46" s="81">
         <f t="shared" si="2"/>
@@ -10561,7 +10441,7 @@
       </c>
       <c r="P46" s="96">
         <f t="shared" si="3"/>
-        <v>1655</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="81"/>
     </row>
@@ -10596,10 +10476,10 @@
         <v>0</v>
       </c>
       <c r="J47" s="97">
-        <v>1207</v>
+        <v>0</v>
       </c>
       <c r="K47" s="97">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="L47" s="97">
         <v>0</v>
@@ -10610,7 +10490,7 @@
       </c>
       <c r="N47" s="97">
         <f t="shared" si="1"/>
-        <v>1559</v>
+        <v>0</v>
       </c>
       <c r="O47" s="80">
         <f t="shared" si="2"/>
@@ -10618,7 +10498,7 @@
       </c>
       <c r="P47" s="97">
         <f t="shared" si="3"/>
-        <v>1559</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="80"/>
     </row>
@@ -10653,10 +10533,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="96">
-        <v>1511</v>
+        <v>0</v>
       </c>
       <c r="K48" s="96">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="L48" s="96">
         <v>0</v>
@@ -10667,7 +10547,7 @@
       </c>
       <c r="N48" s="96">
         <f t="shared" si="1"/>
-        <v>1863</v>
+        <v>0</v>
       </c>
       <c r="O48" s="81">
         <f t="shared" si="2"/>
@@ -10675,7 +10555,7 @@
       </c>
       <c r="P48" s="96">
         <f t="shared" si="3"/>
-        <v>1863</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="81"/>
     </row>
@@ -11097,9 +10977,9 @@
       <c r="K56" s="146"/>
       <c r="L56" s="146"/>
       <c r="M56" s="146"/>
-      <c r="N56" s="167"/>
+      <c r="N56" s="165"/>
       <c r="O56" s="146"/>
-      <c r="P56" s="167"/>
+      <c r="P56" s="165"/>
       <c r="Q56" s="146"/>
     </row>
     <row r="57" spans="1:17" ht="15" x14ac:dyDescent="0.25">
@@ -11112,10 +10992,10 @@
         <v>أ/دعاء عبد الدايم إبراهيم نصار</v>
       </c>
       <c r="C57" s="97">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D57" s="97">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E57" s="97">
         <v>0</v>
@@ -11130,24 +11010,24 @@
         <v>0</v>
       </c>
       <c r="I57" s="97">
-        <v>4313.75</v>
+        <v>0</v>
       </c>
       <c r="J57" s="97">
-        <v>39381</v>
+        <v>0</v>
       </c>
       <c r="K57" s="97">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="L57" s="97">
         <v>0</v>
       </c>
       <c r="M57" s="80">
         <f t="shared" si="0"/>
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="N57" s="97">
         <f t="shared" si="1"/>
-        <v>44284.75</v>
+        <v>0</v>
       </c>
       <c r="O57" s="80">
         <f t="shared" si="2"/>
@@ -11155,7 +11035,7 @@
       </c>
       <c r="P57" s="97">
         <f t="shared" si="3"/>
-        <v>46884.75</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="80"/>
     </row>
@@ -11169,10 +11049,10 @@
         <v>أ/أحمد محمد رزق</v>
       </c>
       <c r="C58" s="96">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D58" s="96">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E58" s="96">
         <v>0</v>
@@ -11187,24 +11067,24 @@
         <v>0</v>
       </c>
       <c r="I58" s="155">
-        <v>4313.75</v>
+        <v>0</v>
       </c>
       <c r="J58" s="96">
-        <v>9559</v>
+        <v>0</v>
       </c>
       <c r="K58" s="96">
-        <v>491</v>
+        <v>0</v>
       </c>
       <c r="L58" s="96">
         <v>0</v>
       </c>
       <c r="M58" s="81">
         <f t="shared" si="0"/>
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="N58" s="96">
         <f t="shared" si="1"/>
-        <v>14363.75</v>
+        <v>0</v>
       </c>
       <c r="O58" s="81">
         <f t="shared" si="2"/>
@@ -11212,7 +11092,7 @@
       </c>
       <c r="P58" s="96">
         <f t="shared" si="3"/>
-        <v>16663.75</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="81"/>
     </row>
@@ -11400,7 +11280,7 @@
         <v>0</v>
       </c>
       <c r="D62" s="96">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="E62" s="96">
         <v>0</v>
@@ -11415,24 +11295,24 @@
         <v>0</v>
       </c>
       <c r="I62" s="155">
-        <v>4313.75</v>
+        <v>0</v>
       </c>
       <c r="J62" s="96">
-        <v>7619</v>
+        <v>0</v>
       </c>
       <c r="K62" s="96">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="L62" s="96">
         <v>0</v>
       </c>
       <c r="M62" s="81">
         <f t="shared" si="0"/>
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="N62" s="96">
         <f t="shared" si="1"/>
-        <v>12522.75</v>
+        <v>0</v>
       </c>
       <c r="O62" s="81">
         <f t="shared" si="2"/>
@@ -11440,7 +11320,7 @@
       </c>
       <c r="P62" s="96">
         <f t="shared" si="3"/>
-        <v>14722.75</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="81"/>
     </row>
@@ -11457,7 +11337,7 @@
         <v>0</v>
       </c>
       <c r="D63" s="97">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E63" s="97">
         <v>0</v>
@@ -11472,24 +11352,24 @@
         <v>0</v>
       </c>
       <c r="I63" s="97">
-        <v>4313.75</v>
+        <v>0</v>
       </c>
       <c r="J63" s="97">
-        <v>5675</v>
+        <v>0</v>
       </c>
       <c r="K63" s="97">
-        <v>872</v>
+        <v>0</v>
       </c>
       <c r="L63" s="97">
         <v>0</v>
       </c>
       <c r="M63" s="80">
         <f t="shared" si="0"/>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="N63" s="97">
         <f t="shared" si="1"/>
-        <v>10860.75</v>
+        <v>0</v>
       </c>
       <c r="O63" s="80">
         <f t="shared" si="2"/>
@@ -11497,7 +11377,7 @@
       </c>
       <c r="P63" s="97">
         <f t="shared" si="3"/>
-        <v>12860.75</v>
+        <v>0</v>
       </c>
       <c r="Q63" s="80"/>
     </row>
@@ -11739,10 +11619,10 @@
         <v>أ/مروة شريف عبدالحميد سلامة</v>
       </c>
       <c r="C68" s="96">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="D68" s="96">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="E68" s="96">
         <v>0</v>
@@ -11757,24 +11637,24 @@
         <v>0</v>
       </c>
       <c r="I68" s="96">
-        <v>4313.75</v>
+        <v>0</v>
       </c>
       <c r="J68" s="96">
-        <v>8474</v>
+        <v>0</v>
       </c>
       <c r="K68" s="96">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="L68" s="96">
         <v>0</v>
       </c>
       <c r="M68" s="81">
         <f t="shared" si="0"/>
-        <v>2405</v>
+        <v>0</v>
       </c>
       <c r="N68" s="96">
         <f t="shared" si="1"/>
-        <v>13460.75</v>
+        <v>0</v>
       </c>
       <c r="O68" s="81">
         <f t="shared" si="2"/>
@@ -11782,7 +11662,7 @@
       </c>
       <c r="P68" s="96">
         <f t="shared" si="3"/>
-        <v>15865.75</v>
+        <v>0</v>
       </c>
       <c r="Q68" s="81"/>
     </row>
@@ -11799,7 +11679,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="97">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="E69" s="97">
         <v>0</v>
@@ -11814,24 +11694,24 @@
         <v>0</v>
       </c>
       <c r="I69" s="97">
-        <v>4118.8900000000003</v>
+        <v>0</v>
       </c>
       <c r="J69" s="97">
-        <v>2331</v>
+        <v>0</v>
       </c>
       <c r="K69" s="97">
-        <v>1422</v>
+        <v>0</v>
       </c>
       <c r="L69" s="97">
         <v>0</v>
       </c>
       <c r="M69" s="80">
         <f t="shared" ref="M69:M100" si="4">SUM(C69:E69)+L69</f>
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="N69" s="97">
         <f t="shared" ref="N69:N100" si="5">SUM(I69:K69)</f>
-        <v>7871.89</v>
+        <v>0</v>
       </c>
       <c r="O69" s="80">
         <f t="shared" ref="O69:O100" si="6">SUM(G69:H69)</f>
@@ -11839,16 +11719,16 @@
       </c>
       <c r="P69" s="97">
         <f t="shared" ref="P69:P100" si="7">SUM(M69:O69)</f>
-        <v>9971.89</v>
+        <v>0</v>
       </c>
       <c r="Q69" s="80"/>
     </row>
     <row r="70" spans="1:17" ht="15" x14ac:dyDescent="0.25">
-      <c r="A70" s="193">
+      <c r="A70" s="172">
         <f>مرتبات!A70</f>
         <v>0</v>
       </c>
-      <c r="B70" s="194" t="str">
+      <c r="B70" s="173" t="str">
         <f>مرتبات!B70</f>
         <v xml:space="preserve">أ/أحمد سمير حسن السيد </v>
       </c>
@@ -11871,7 +11751,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="157">
-        <v>3433.01</v>
+        <v>0</v>
       </c>
       <c r="J70" s="157">
         <v>0</v>
@@ -11882,24 +11762,24 @@
       <c r="L70" s="157">
         <v>0</v>
       </c>
-      <c r="M70" s="195">
+      <c r="M70" s="174">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N70" s="157">
         <f t="shared" si="5"/>
-        <v>3433.01</v>
-      </c>
-      <c r="O70" s="195">
+        <v>0</v>
+      </c>
+      <c r="O70" s="174">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P70" s="157">
         <f t="shared" si="7"/>
-        <v>3433.01</v>
-      </c>
-      <c r="Q70" s="195" t="s">
-        <v>155</v>
+        <v>0</v>
+      </c>
+      <c r="Q70" s="174" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="71" spans="1:17" ht="15" x14ac:dyDescent="0.25">
@@ -11915,7 +11795,7 @@
         <v>0</v>
       </c>
       <c r="D71" s="97">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E71" s="97">
         <v>0</v>
@@ -11929,25 +11809,25 @@
       <c r="H71" s="97">
         <v>0</v>
       </c>
-      <c r="I71" s="196">
+      <c r="I71" s="175">
         <v>0</v>
       </c>
       <c r="J71" s="97">
-        <v>3634</v>
+        <v>0</v>
       </c>
       <c r="K71" s="97">
-        <v>1422</v>
+        <v>0</v>
       </c>
       <c r="L71" s="97">
         <v>0</v>
       </c>
       <c r="M71" s="80">
         <f t="shared" si="4"/>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="N71" s="97">
         <f t="shared" si="5"/>
-        <v>5056</v>
+        <v>0</v>
       </c>
       <c r="O71" s="80">
         <f t="shared" si="6"/>
@@ -11955,7 +11835,7 @@
       </c>
       <c r="P71" s="97">
         <f t="shared" si="7"/>
-        <v>7056</v>
+        <v>0</v>
       </c>
       <c r="Q71" s="80"/>
     </row>
@@ -11972,7 +11852,7 @@
         <v>0</v>
       </c>
       <c r="D72" s="96">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="E72" s="96">
         <v>0</v>
@@ -11987,24 +11867,24 @@
         <v>0</v>
       </c>
       <c r="I72" s="96">
-        <v>4313.75</v>
+        <v>0</v>
       </c>
       <c r="J72" s="96">
-        <v>3505</v>
+        <v>0</v>
       </c>
       <c r="K72" s="96">
-        <v>1195</v>
+        <v>0</v>
       </c>
       <c r="L72" s="96">
         <v>0</v>
       </c>
       <c r="M72" s="81">
         <f t="shared" si="4"/>
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="N72" s="96">
         <f t="shared" si="5"/>
-        <v>9013.75</v>
+        <v>0</v>
       </c>
       <c r="O72" s="81">
         <f t="shared" si="6"/>
@@ -12012,7 +11892,7 @@
       </c>
       <c r="P72" s="96">
         <f t="shared" si="7"/>
-        <v>11113.75</v>
+        <v>0</v>
       </c>
       <c r="Q72" s="81"/>
     </row>
@@ -12029,7 +11909,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="97">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E73" s="97">
         <v>0</v>
@@ -12044,24 +11924,24 @@
         <v>0</v>
       </c>
       <c r="I73" s="97">
-        <v>3433.15</v>
+        <v>0</v>
       </c>
       <c r="J73" s="97">
-        <v>1907</v>
+        <v>0</v>
       </c>
       <c r="K73" s="97">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="L73" s="97">
         <v>0</v>
       </c>
       <c r="M73" s="80">
         <f t="shared" si="4"/>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="N73" s="97">
         <f t="shared" si="5"/>
-        <v>5930.15</v>
+        <v>0</v>
       </c>
       <c r="O73" s="80">
         <f t="shared" si="6"/>
@@ -12069,7 +11949,7 @@
       </c>
       <c r="P73" s="97">
         <f t="shared" si="7"/>
-        <v>7930.15</v>
+        <v>0</v>
       </c>
       <c r="Q73" s="80"/>
     </row>
@@ -12083,10 +11963,10 @@
         <v>أ/سامي ابراهيم محمد</v>
       </c>
       <c r="C74" s="96">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="D74" s="96">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="E74" s="96">
         <v>0</v>
@@ -12101,24 +11981,24 @@
         <v>0</v>
       </c>
       <c r="I74" s="96">
-        <v>3433.15</v>
+        <v>0</v>
       </c>
       <c r="J74" s="96">
-        <v>1918</v>
+        <v>0</v>
       </c>
       <c r="K74" s="96">
-        <v>872</v>
+        <v>0</v>
       </c>
       <c r="L74" s="96">
         <v>0</v>
       </c>
       <c r="M74" s="81">
         <f t="shared" si="4"/>
-        <v>2415</v>
+        <v>0</v>
       </c>
       <c r="N74" s="96">
         <f t="shared" si="5"/>
-        <v>6223.15</v>
+        <v>0</v>
       </c>
       <c r="O74" s="81">
         <f t="shared" si="6"/>
@@ -12126,7 +12006,7 @@
       </c>
       <c r="P74" s="96">
         <f t="shared" si="7"/>
-        <v>8638.15</v>
+        <v>0</v>
       </c>
       <c r="Q74" s="81"/>
     </row>
@@ -12140,10 +12020,10 @@
         <v>أ/محمود على محمود حسين</v>
       </c>
       <c r="C75" s="97">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="D75" s="97">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E75" s="97">
         <v>0</v>
@@ -12158,24 +12038,24 @@
         <v>0</v>
       </c>
       <c r="I75" s="97">
-        <v>3204</v>
+        <v>0</v>
       </c>
       <c r="J75" s="97">
-        <v>1776</v>
+        <v>0</v>
       </c>
       <c r="K75" s="96">
-        <v>872</v>
+        <v>0</v>
       </c>
       <c r="L75" s="97">
         <v>0</v>
       </c>
       <c r="M75" s="80">
         <f t="shared" si="4"/>
-        <v>2315</v>
+        <v>0</v>
       </c>
       <c r="N75" s="97">
         <f t="shared" si="5"/>
-        <v>5852</v>
+        <v>0</v>
       </c>
       <c r="O75" s="80">
         <f t="shared" si="6"/>
@@ -12183,7 +12063,7 @@
       </c>
       <c r="P75" s="97">
         <f t="shared" si="7"/>
-        <v>8167</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="80"/>
     </row>
@@ -12200,7 +12080,7 @@
         <v>0</v>
       </c>
       <c r="D76" s="96">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="E76" s="96">
         <v>0</v>
@@ -12215,24 +12095,24 @@
         <v>0</v>
       </c>
       <c r="I76" s="96">
-        <v>3089</v>
+        <v>0</v>
       </c>
       <c r="J76" s="96">
-        <v>1657</v>
+        <v>0</v>
       </c>
       <c r="K76" s="96">
-        <v>872</v>
+        <v>0</v>
       </c>
       <c r="L76" s="96">
         <v>0</v>
       </c>
       <c r="M76" s="81">
         <f t="shared" si="4"/>
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="N76" s="96">
         <f t="shared" si="5"/>
-        <v>5618</v>
+        <v>0</v>
       </c>
       <c r="O76" s="81">
         <f t="shared" si="6"/>
@@ -12240,7 +12120,7 @@
       </c>
       <c r="P76" s="96">
         <f t="shared" si="7"/>
-        <v>8118</v>
+        <v>0</v>
       </c>
       <c r="Q76" s="81"/>
     </row>
@@ -12257,7 +12137,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="97">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E77" s="97">
         <v>0</v>
@@ -12272,24 +12152,24 @@
         <v>0</v>
       </c>
       <c r="I77" s="97">
-        <v>2745</v>
+        <v>0</v>
       </c>
       <c r="J77" s="97">
-        <v>1354</v>
+        <v>0</v>
       </c>
       <c r="K77" s="97">
-        <v>673</v>
+        <v>0</v>
       </c>
       <c r="L77" s="97">
         <v>0</v>
       </c>
       <c r="M77" s="80">
         <f t="shared" si="4"/>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="N77" s="97">
         <f t="shared" si="5"/>
-        <v>4772</v>
+        <v>0</v>
       </c>
       <c r="O77" s="80">
         <f t="shared" si="6"/>
@@ -12297,7 +12177,7 @@
       </c>
       <c r="P77" s="97">
         <f t="shared" si="7"/>
-        <v>6772</v>
+        <v>0</v>
       </c>
       <c r="Q77" s="80"/>
     </row>
@@ -12314,10 +12194,10 @@
         <v>0</v>
       </c>
       <c r="D78" s="96">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E78" s="96">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F78" s="96">
         <v>0</v>
@@ -12329,24 +12209,24 @@
         <v>0</v>
       </c>
       <c r="I78" s="96">
-        <v>2518</v>
+        <v>0</v>
       </c>
       <c r="J78" s="96">
-        <v>1180</v>
+        <v>0</v>
       </c>
       <c r="K78" s="96">
-        <v>1195</v>
+        <v>0</v>
       </c>
       <c r="L78" s="96">
         <v>0</v>
       </c>
       <c r="M78" s="81">
         <f t="shared" si="4"/>
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="N78" s="96">
         <f t="shared" si="5"/>
-        <v>4893</v>
+        <v>0</v>
       </c>
       <c r="O78" s="81">
         <f t="shared" si="6"/>
@@ -12354,7 +12234,7 @@
       </c>
       <c r="P78" s="96">
         <f t="shared" si="7"/>
-        <v>7193</v>
+        <v>0</v>
       </c>
       <c r="Q78" s="81"/>
     </row>
@@ -12371,7 +12251,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="97">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="E79" s="97">
         <v>0</v>
@@ -12386,24 +12266,24 @@
         <v>0</v>
       </c>
       <c r="I79" s="97">
-        <v>2518</v>
+        <v>0</v>
       </c>
       <c r="J79" s="97">
-        <v>1180</v>
+        <v>0</v>
       </c>
       <c r="K79" s="97">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="L79" s="97">
         <v>0</v>
       </c>
       <c r="M79" s="80">
         <f t="shared" si="4"/>
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="N79" s="97">
         <f t="shared" si="5"/>
-        <v>4288</v>
+        <v>0</v>
       </c>
       <c r="O79" s="80">
         <f t="shared" si="6"/>
@@ -12411,7 +12291,7 @@
       </c>
       <c r="P79" s="97">
         <f t="shared" si="7"/>
-        <v>6488</v>
+        <v>0</v>
       </c>
       <c r="Q79" s="80"/>
     </row>
@@ -12482,10 +12362,10 @@
         <v>أ/محمد عبدالجواد محمد</v>
       </c>
       <c r="C81" s="97">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="D81" s="97">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="E81" s="97">
         <v>0</v>
@@ -12500,24 +12380,24 @@
         <v>0</v>
       </c>
       <c r="I81" s="97">
-        <v>3662</v>
+        <v>0</v>
       </c>
       <c r="J81" s="97">
-        <v>2323</v>
+        <v>0</v>
       </c>
       <c r="K81" s="97">
-        <v>872</v>
+        <v>0</v>
       </c>
       <c r="L81" s="97">
         <v>0</v>
       </c>
       <c r="M81" s="80">
         <f t="shared" si="4"/>
-        <v>2550</v>
+        <v>0</v>
       </c>
       <c r="N81" s="97">
         <f t="shared" si="5"/>
-        <v>6857</v>
+        <v>0</v>
       </c>
       <c r="O81" s="80">
         <f t="shared" si="6"/>
@@ -12525,7 +12405,7 @@
       </c>
       <c r="P81" s="97">
         <f t="shared" si="7"/>
-        <v>9407</v>
+        <v>0</v>
       </c>
       <c r="Q81" s="80"/>
     </row>
@@ -12542,7 +12422,7 @@
         <v>0</v>
       </c>
       <c r="D82" s="96">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E82" s="96">
         <v>0</v>
@@ -12557,24 +12437,24 @@
         <v>0</v>
       </c>
       <c r="I82" s="96">
-        <v>2290</v>
+        <v>0</v>
       </c>
       <c r="J82" s="96">
-        <v>930</v>
+        <v>0</v>
       </c>
       <c r="K82" s="96">
-        <v>491</v>
+        <v>0</v>
       </c>
       <c r="L82" s="96">
         <v>0</v>
       </c>
       <c r="M82" s="81">
         <f t="shared" si="4"/>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="N82" s="96">
         <f t="shared" si="5"/>
-        <v>3711</v>
+        <v>0</v>
       </c>
       <c r="O82" s="81">
         <f t="shared" si="6"/>
@@ -12582,7 +12462,7 @@
       </c>
       <c r="P82" s="96">
         <f t="shared" si="7"/>
-        <v>5711</v>
+        <v>0</v>
       </c>
       <c r="Q82" s="81"/>
     </row>
@@ -12599,7 +12479,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="97">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E83" s="97">
         <v>0</v>
@@ -12614,24 +12494,24 @@
         <v>0</v>
       </c>
       <c r="I83" s="97">
-        <v>1602</v>
+        <v>0</v>
       </c>
       <c r="J83" s="97">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="K83" s="97">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="L83" s="97">
         <v>0</v>
       </c>
       <c r="M83" s="80">
         <f t="shared" si="4"/>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="N83" s="97">
         <f t="shared" si="5"/>
-        <v>2286</v>
+        <v>0</v>
       </c>
       <c r="O83" s="80">
         <f t="shared" si="6"/>
@@ -12639,7 +12519,7 @@
       </c>
       <c r="P83" s="97">
         <f t="shared" si="7"/>
-        <v>4286</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="80"/>
     </row>
@@ -12655,7 +12535,7 @@
       <c r="C84" s="96">
         <v>0</v>
       </c>
-      <c r="D84" s="207">
+      <c r="D84" s="178">
         <v>0</v>
       </c>
       <c r="E84" s="96">
@@ -12671,10 +12551,10 @@
         <v>0</v>
       </c>
       <c r="I84" s="96">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="J84" s="96">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K84" s="96">
         <v>0</v>
@@ -12688,7 +12568,7 @@
       </c>
       <c r="N84" s="96">
         <f t="shared" si="5"/>
-        <v>1102</v>
+        <v>0</v>
       </c>
       <c r="O84" s="81">
         <f t="shared" si="6"/>
@@ -12696,7 +12576,7 @@
       </c>
       <c r="P84" s="96">
         <f t="shared" si="7"/>
-        <v>1102</v>
+        <v>0</v>
       </c>
       <c r="Q84" s="81"/>
     </row>
@@ -12713,7 +12593,7 @@
         <v>0</v>
       </c>
       <c r="D85" s="97">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="E85" s="97">
         <v>0</v>
@@ -12728,10 +12608,10 @@
         <v>0</v>
       </c>
       <c r="I85" s="97">
-        <v>3867.5</v>
+        <v>0</v>
       </c>
       <c r="J85" s="97">
-        <v>1304</v>
+        <v>0</v>
       </c>
       <c r="K85" s="97">
         <v>0</v>
@@ -12741,11 +12621,11 @@
       </c>
       <c r="M85" s="80">
         <f t="shared" si="4"/>
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="N85" s="97">
         <f t="shared" si="5"/>
-        <v>5171.5</v>
+        <v>0</v>
       </c>
       <c r="O85" s="80">
         <f t="shared" si="6"/>
@@ -12753,7 +12633,7 @@
       </c>
       <c r="P85" s="97">
         <f t="shared" si="7"/>
-        <v>7271.5</v>
+        <v>0</v>
       </c>
       <c r="Q85" s="80"/>
     </row>
@@ -13630,9 +13510,9 @@
       <c r="K101" s="146"/>
       <c r="L101" s="146"/>
       <c r="M101" s="146"/>
-      <c r="N101" s="167"/>
+      <c r="N101" s="165"/>
       <c r="O101" s="146"/>
-      <c r="P101" s="167"/>
+      <c r="P101" s="165"/>
       <c r="Q101" s="146"/>
     </row>
     <row r="102" spans="1:17" ht="15" x14ac:dyDescent="0.25">
@@ -13837,7 +13717,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="97">
-        <v>3045</v>
+        <v>0</v>
       </c>
       <c r="K105" s="97">
         <v>0</v>
@@ -13851,7 +13731,7 @@
       </c>
       <c r="N105" s="97">
         <f t="shared" si="9"/>
-        <v>3045</v>
+        <v>0</v>
       </c>
       <c r="O105" s="80">
         <f t="shared" si="10"/>
@@ -13859,7 +13739,7 @@
       </c>
       <c r="P105" s="97">
         <f t="shared" si="11"/>
-        <v>3045</v>
+        <v>0</v>
       </c>
       <c r="Q105" s="80"/>
     </row>
@@ -13983,7 +13863,7 @@
         <v>7</v>
       </c>
       <c r="B108" s="82" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C108" s="96">
         <v>0</v>
@@ -14556,15 +14436,15 @@
       </c>
       <c r="C118" s="89">
         <f t="shared" ref="C118:L118" si="12">SUM(C4:C17)+SUM(C19:C55)+SUM(C57:C100)+SUM(C102:C117)</f>
-        <v>4925</v>
+        <v>0</v>
       </c>
       <c r="D118" s="89">
         <f t="shared" si="12"/>
-        <v>39600</v>
+        <v>0</v>
       </c>
       <c r="E118" s="89">
         <f t="shared" si="12"/>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F118" s="89">
         <f t="shared" si="12"/>
@@ -14576,19 +14456,19 @@
       </c>
       <c r="H118" s="89">
         <f t="shared" si="12"/>
-        <v>5250</v>
+        <v>0</v>
       </c>
       <c r="I118" s="89">
         <f t="shared" si="12"/>
-        <v>72146.200000000012</v>
+        <v>0</v>
       </c>
       <c r="J118" s="89">
         <f t="shared" si="12"/>
-        <v>387155</v>
+        <v>0</v>
       </c>
       <c r="K118" s="89">
         <f t="shared" si="12"/>
-        <v>25868</v>
+        <v>0</v>
       </c>
       <c r="L118" s="89">
         <f t="shared" si="12"/>
@@ -14596,19 +14476,19 @@
       </c>
       <c r="M118" s="89">
         <f t="shared" si="8"/>
-        <v>44825</v>
+        <v>0</v>
       </c>
       <c r="N118" s="89">
         <f t="shared" si="9"/>
-        <v>485169.2</v>
+        <v>0</v>
       </c>
       <c r="O118" s="90">
         <f t="shared" si="10"/>
-        <v>5250</v>
+        <v>0</v>
       </c>
       <c r="P118" s="89">
         <f t="shared" si="11"/>
-        <v>535244.19999999995</v>
+        <v>0</v>
       </c>
       <c r="Q118" s="91"/>
     </row>
@@ -14653,8 +14533,8 @@
       <c r="A2" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="179" t="s">
-        <v>151</v>
+      <c r="B2" s="168" t="s">
+        <v>149</v>
       </c>
       <c r="C2" s="143" t="s">
         <v>47</v>
@@ -14812,7 +14692,9 @@
       <c r="F6" s="64">
         <v>0</v>
       </c>
-      <c r="G6" s="64"/>
+      <c r="G6" s="64">
+        <v>0</v>
+      </c>
       <c r="H6" s="64">
         <v>0</v>
       </c>
@@ -15377,7 +15259,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="64">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="H20" s="64">
         <v>0</v>
@@ -15386,14 +15268,14 @@
         <v>0</v>
       </c>
       <c r="J20" s="64">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K20" s="64">
         <v>0</v>
       </c>
       <c r="L20" s="64">
         <f t="shared" si="0"/>
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="M20" s="72"/>
     </row>
@@ -15418,7 +15300,9 @@
       <c r="F21" s="64">
         <v>0</v>
       </c>
-      <c r="G21" s="64"/>
+      <c r="G21" s="64">
+        <v>0</v>
+      </c>
       <c r="H21" s="64">
         <v>0</v>
       </c>
@@ -15437,7 +15321,7 @@
       </c>
       <c r="M21" s="23"/>
     </row>
-    <row r="22" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="98">
         <f>مرتبات!A22</f>
         <v>4</v>
@@ -15462,24 +15346,22 @@
         <v>0</v>
       </c>
       <c r="H22" s="95">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="I22" s="95">
-        <v>4600</v>
-      </c>
-      <c r="J22" s="208">
-        <v>200</v>
+        <v>0</v>
+      </c>
+      <c r="J22" s="179">
+        <v>0</v>
       </c>
       <c r="K22" s="64">
         <v>0</v>
       </c>
       <c r="L22" s="95">
         <f t="shared" si="0"/>
-        <v>7100</v>
-      </c>
-      <c r="M22" s="206" t="s">
-        <v>158</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M22" s="177"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="98">
@@ -15551,7 +15433,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="64">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J24" s="64">
         <v>0</v>
@@ -15561,11 +15443,9 @@
       </c>
       <c r="L24" s="64">
         <f t="shared" si="0"/>
-        <v>2000</v>
-      </c>
-      <c r="M24" s="73" t="s">
-        <v>161</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M24" s="73"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="98">
@@ -15589,7 +15469,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="64">
-        <v>487</v>
+        <v>0</v>
       </c>
       <c r="H25" s="64">
         <v>0</v>
@@ -15598,12 +15478,14 @@
         <v>0</v>
       </c>
       <c r="J25" s="64">
-        <v>200</v>
-      </c>
-      <c r="K25" s="64"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="64">
+        <v>0</v>
+      </c>
       <c r="L25" s="64">
         <f t="shared" si="0"/>
-        <v>687</v>
+        <v>0</v>
       </c>
       <c r="M25" s="23"/>
     </row>
@@ -16405,7 +16287,7 @@
       </c>
       <c r="M44" s="23"/>
     </row>
-    <row r="45" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="98">
         <f>مرتبات!A45</f>
         <v>11</v>
@@ -16430,10 +16312,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="95">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="I45" s="95">
-        <v>1467</v>
+        <v>0</v>
       </c>
       <c r="J45" s="64">
         <v>0</v>
@@ -16443,11 +16325,9 @@
       </c>
       <c r="L45" s="95">
         <f t="shared" si="0"/>
-        <v>1834</v>
-      </c>
-      <c r="M45" s="206" t="s">
-        <v>159</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M45" s="177"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="98">
@@ -16477,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="64">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="J46" s="64">
         <v>0</v>
@@ -16487,55 +16367,51 @@
       </c>
       <c r="L46" s="64">
         <f t="shared" si="0"/>
-        <v>333</v>
-      </c>
-      <c r="M46" s="72" t="s">
-        <v>162</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M46" s="72"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="98">
         <f>مرتبات!A47</f>
         <v>13</v>
       </c>
-      <c r="B47" s="203" t="str">
+      <c r="B47" s="19" t="str">
         <f>مرتبات!B47</f>
         <v>أ/ليلي امين محمد امين طموم</v>
       </c>
-      <c r="C47" s="204">
-        <v>0</v>
-      </c>
-      <c r="D47" s="204">
-        <v>0</v>
-      </c>
-      <c r="E47" s="204">
-        <v>0</v>
-      </c>
-      <c r="F47" s="204">
-        <v>6333</v>
-      </c>
-      <c r="G47" s="204">
-        <v>0</v>
-      </c>
-      <c r="H47" s="204">
-        <v>0</v>
-      </c>
-      <c r="I47" s="204">
-        <v>0</v>
-      </c>
-      <c r="J47" s="204">
-        <v>0</v>
-      </c>
-      <c r="K47" s="204">
-        <v>0</v>
-      </c>
-      <c r="L47" s="204">
+      <c r="C47" s="64">
+        <v>0</v>
+      </c>
+      <c r="D47" s="64">
+        <v>0</v>
+      </c>
+      <c r="E47" s="64">
+        <v>0</v>
+      </c>
+      <c r="F47" s="64">
+        <v>0</v>
+      </c>
+      <c r="G47" s="64">
+        <v>0</v>
+      </c>
+      <c r="H47" s="64">
+        <v>0</v>
+      </c>
+      <c r="I47" s="64">
+        <v>0</v>
+      </c>
+      <c r="J47" s="64">
+        <v>0</v>
+      </c>
+      <c r="K47" s="64">
+        <v>0</v>
+      </c>
+      <c r="L47" s="64">
         <f t="shared" si="0"/>
-        <v>6333</v>
-      </c>
-      <c r="M47" s="205" t="s">
-        <v>157</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M47" s="83"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="98">
@@ -16565,21 +16441,19 @@
         <v>0</v>
       </c>
       <c r="I48" s="64">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="J48" s="64">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="K48" s="64">
         <v>0</v>
       </c>
       <c r="L48" s="64">
         <f t="shared" si="0"/>
-        <v>1750</v>
-      </c>
-      <c r="M48" s="159" t="s">
-        <v>160</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M48" s="159"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="98">
@@ -16876,7 +16750,7 @@
       <c r="M55" s="83"/>
     </row>
     <row r="56" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="178">
+      <c r="A56" s="167">
         <f>مرتبات!A56</f>
         <v>15</v>
       </c>
@@ -16911,9 +16785,11 @@
         <v>0</v>
       </c>
       <c r="E57" s="64">
-        <v>10000</v>
-      </c>
-      <c r="F57" s="64"/>
+        <v>0</v>
+      </c>
+      <c r="F57" s="64">
+        <v>0</v>
+      </c>
       <c r="G57" s="64">
         <v>0</v>
       </c>
@@ -16931,7 +16807,7 @@
       </c>
       <c r="L57" s="64">
         <f t="shared" si="0"/>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="M57" s="160"/>
     </row>
@@ -17113,7 +16989,7 @@
         <v>أ/خالد محمد حلمى</v>
       </c>
       <c r="C62" s="64">
-        <v>634.5</v>
+        <v>0</v>
       </c>
       <c r="D62" s="64">
         <v>0</v>
@@ -17141,11 +17017,9 @@
       </c>
       <c r="L62" s="64">
         <f t="shared" si="0"/>
-        <v>634.5</v>
-      </c>
-      <c r="M62" s="158" t="s">
-        <v>156</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M62" s="158"/>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="98">
@@ -17445,40 +17319,42 @@
       <c r="A70" s="98">
         <v>0</v>
       </c>
-      <c r="B70" s="183" t="str">
+      <c r="B70" s="19" t="str">
         <f>مرتبات!B70</f>
         <v xml:space="preserve">أ/أحمد سمير حسن السيد </v>
       </c>
-      <c r="C70" s="184"/>
-      <c r="D70" s="184">
-        <v>0</v>
-      </c>
-      <c r="E70" s="184">
-        <v>0</v>
-      </c>
-      <c r="F70" s="184">
-        <v>0</v>
-      </c>
-      <c r="G70" s="184">
-        <v>0</v>
-      </c>
-      <c r="H70" s="184">
-        <v>0</v>
-      </c>
-      <c r="I70" s="184">
-        <v>0</v>
-      </c>
-      <c r="J70" s="184">
-        <v>0</v>
-      </c>
-      <c r="K70" s="184">
-        <v>0</v>
-      </c>
-      <c r="L70" s="184">
+      <c r="C70" s="64">
+        <v>0</v>
+      </c>
+      <c r="D70" s="64">
+        <v>0</v>
+      </c>
+      <c r="E70" s="64">
+        <v>0</v>
+      </c>
+      <c r="F70" s="64">
+        <v>0</v>
+      </c>
+      <c r="G70" s="64">
+        <v>0</v>
+      </c>
+      <c r="H70" s="64">
+        <v>0</v>
+      </c>
+      <c r="I70" s="64">
+        <v>0</v>
+      </c>
+      <c r="J70" s="64">
+        <v>0</v>
+      </c>
+      <c r="K70" s="64">
+        <v>0</v>
+      </c>
+      <c r="L70" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M70" s="185"/>
+      <c r="M70" s="83"/>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="98">
@@ -17530,7 +17406,7 @@
         <v>أ/شريف شكرى محمد</v>
       </c>
       <c r="C72" s="64">
-        <v>1286</v>
+        <v>0</v>
       </c>
       <c r="D72" s="64">
         <v>0</v>
@@ -17558,11 +17434,9 @@
       </c>
       <c r="L72" s="64">
         <f t="shared" si="1"/>
-        <v>1286</v>
-      </c>
-      <c r="M72" s="158" t="s">
-        <v>156</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M72" s="158"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="98">
@@ -17849,7 +17723,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M79" s="165"/>
+      <c r="M79" s="164"/>
     </row>
     <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="98">
@@ -18049,11 +17923,11 @@
         <v>0</v>
       </c>
       <c r="K84" s="64">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="L84" s="64">
         <f t="shared" si="1"/>
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="M84" s="83"/>
     </row>
@@ -18062,7 +17936,7 @@
         <v>20</v>
       </c>
       <c r="B85" s="19" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C85" s="64">
         <v>0</v>
@@ -18080,7 +17954,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="64">
-        <v>9100</v>
+        <v>0</v>
       </c>
       <c r="I85" s="64">
         <v>0</v>
@@ -18093,11 +17967,9 @@
       </c>
       <c r="L85" s="64">
         <f t="shared" si="1"/>
-        <v>9100</v>
-      </c>
-      <c r="M85" s="73" t="s">
-        <v>164</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M85" s="73"/>
     </row>
     <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="98">
@@ -18730,8 +18602,7 @@
       <c r="M100" s="83"/>
     </row>
     <row r="101" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A101" s="177">
-        <f>مرتبات!A101</f>
+      <c r="A101" s="98">
         <v>20</v>
       </c>
       <c r="B101" s="140" t="s">
@@ -18917,7 +18788,7 @@
       </c>
       <c r="M105" s="83"/>
     </row>
-    <row r="106" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="98">
         <f>مرتبات!A106</f>
         <v>5</v>
@@ -18938,8 +18809,8 @@
       <c r="F106" s="64">
         <v>0</v>
       </c>
-      <c r="G106" s="182">
-        <v>1227</v>
+      <c r="G106" s="64">
+        <v>0</v>
       </c>
       <c r="H106" s="64">
         <v>0</v>
@@ -18955,7 +18826,7 @@
       </c>
       <c r="L106" s="64">
         <f t="shared" si="1"/>
-        <v>1227</v>
+        <v>0</v>
       </c>
       <c r="M106" s="83"/>
     </row>
@@ -19429,7 +19300,7 @@
       </c>
       <c r="C118" s="94">
         <f>SUM(C4:C17)+SUM(C19:C55)+SUM(C57:C100)+SUM(C102:C117)</f>
-        <v>1920.5</v>
+        <v>0</v>
       </c>
       <c r="D118" s="94">
         <f t="shared" ref="D118:K118" si="2">SUM(D4:D17)+SUM(D19:D55)+SUM(D57:D100)+SUM(D102:D117)</f>
@@ -19437,35 +19308,35 @@
       </c>
       <c r="E118" s="94">
         <f t="shared" si="2"/>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F118" s="94">
         <f t="shared" si="2"/>
-        <v>6333</v>
+        <v>0</v>
       </c>
       <c r="G118" s="94">
         <f t="shared" si="2"/>
-        <v>1827</v>
+        <v>0</v>
       </c>
       <c r="H118" s="94">
         <f>SUM(H4:H17)+SUM(H19:H55)+SUM(H57:H100)+SUM(H102:H117)</f>
-        <v>11767</v>
+        <v>0</v>
       </c>
       <c r="I118" s="94">
         <f t="shared" si="2"/>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="J118" s="94">
         <f t="shared" si="2"/>
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="K118" s="94">
         <f t="shared" si="2"/>
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="L118" s="94">
         <f>SUM(C118:K118)</f>
-        <v>46297.5</v>
+        <v>0</v>
       </c>
       <c r="M118" s="92"/>
     </row>
@@ -19576,10 +19447,10 @@
     </row>
     <row r="3" spans="2:8" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="38"/>
-      <c r="C3" s="217"/>
-      <c r="D3" s="218"/>
-      <c r="E3" s="218"/>
-      <c r="F3" s="219"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="189"/>
+      <c r="E3" s="189"/>
+      <c r="F3" s="190"/>
       <c r="G3" s="39"/>
       <c r="H3" s="40" t="s">
         <v>27</v>
@@ -19611,25 +19482,25 @@
       <c r="C5" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="220">
+      <c r="D5" s="191">
         <f>SUM((INDEX(مرتبات!D1:D1066,H4,1)),VALUE((INDEX(مرتبات!G1:G1066,H4,1))))</f>
-        <v>16000</v>
-      </c>
-      <c r="E5" s="221"/>
-      <c r="F5" s="222"/>
+        <v>0</v>
+      </c>
+      <c r="E5" s="192"/>
+      <c r="F5" s="193"/>
       <c r="G5" s="39"/>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="2:8" ht="13.8" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B6" s="38"/>
-      <c r="C6" s="223" t="s">
+      <c r="C6" s="194" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="224"/>
-      <c r="E6" s="223" t="s">
+      <c r="D6" s="195"/>
+      <c r="E6" s="194" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="224"/>
+      <c r="F6" s="195"/>
       <c r="G6" s="39"/>
       <c r="H6" s="5"/>
     </row>
@@ -19640,7 +19511,7 @@
       </c>
       <c r="D7" s="42">
         <f>INDEX(اضافات!C1:C1069,H4,1)</f>
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="E7" s="41" t="s">
         <v>7</v>
@@ -19659,7 +19530,7 @@
       </c>
       <c r="D8" s="42">
         <f>INDEX(اضافات!D1:D1069,H4,1)</f>
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="E8" s="44" t="s">
         <v>4</v>
@@ -19712,11 +19583,11 @@
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="38"/>
       <c r="C11" s="45" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" s="42">
         <f>INDEX(اضافات!J1:J1069,H4,1)</f>
-        <v>2323</v>
+        <v>0</v>
       </c>
       <c r="E11" s="45" t="s">
         <v>24</v>
@@ -19735,7 +19606,7 @@
       </c>
       <c r="D12" s="42">
         <f>INDEX(اضافات!I1:I1069,H4,1)</f>
-        <v>3662</v>
+        <v>0</v>
       </c>
       <c r="E12" s="45" t="s">
         <v>10</v>
@@ -19754,7 +19625,7 @@
       </c>
       <c r="D13" s="42">
         <f>INDEX(اضافات!K1:K1069,H4,1)</f>
-        <v>872</v>
+        <v>0</v>
       </c>
       <c r="E13" s="45" t="s">
         <v>15</v>
@@ -19799,12 +19670,12 @@
       <c r="C16" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="220">
+      <c r="D16" s="191">
         <f>D5+D7+D8+D9+D10+D11+D12+D13</f>
-        <v>25407</v>
-      </c>
-      <c r="E16" s="221"/>
-      <c r="F16" s="222"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="192"/>
+      <c r="F16" s="193"/>
       <c r="G16" s="39"/>
       <c r="H16" s="5"/>
     </row>
@@ -19813,12 +19684,12 @@
       <c r="C17" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="220">
+      <c r="D17" s="191">
         <f>SUM(D7:D15)</f>
-        <v>9407</v>
-      </c>
-      <c r="E17" s="221"/>
-      <c r="F17" s="222"/>
+        <v>0</v>
+      </c>
+      <c r="E17" s="192"/>
+      <c r="F17" s="193"/>
       <c r="G17" s="39"/>
       <c r="H17" s="5"/>
     </row>
@@ -19827,12 +19698,12 @@
       <c r="C18" s="47" t="s">
         <v>80</v>
       </c>
-      <c r="D18" s="211">
+      <c r="D18" s="182">
         <f>(SUM(F7:F15))</f>
         <v>0</v>
       </c>
-      <c r="E18" s="212"/>
-      <c r="F18" s="213"/>
+      <c r="E18" s="183"/>
+      <c r="F18" s="184"/>
       <c r="G18" s="39"/>
       <c r="H18" s="5"/>
     </row>
@@ -19841,12 +19712,12 @@
       <c r="C19" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="214">
+      <c r="D19" s="185">
         <f>D16-D17-D18</f>
-        <v>16000</v>
-      </c>
-      <c r="E19" s="215"/>
-      <c r="F19" s="216"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="186"/>
+      <c r="F19" s="187"/>
       <c r="G19" s="39"/>
       <c r="H19" s="5"/>
     </row>
@@ -19912,10 +19783,10 @@
     </row>
     <row r="3" spans="2:8" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="38"/>
-      <c r="C3" s="217"/>
-      <c r="D3" s="218"/>
-      <c r="E3" s="218"/>
-      <c r="F3" s="219"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="189"/>
+      <c r="E3" s="189"/>
+      <c r="F3" s="190"/>
       <c r="G3" s="39"/>
       <c r="H3" s="40" t="s">
         <v>27</v>
@@ -19947,25 +19818,25 @@
       <c r="C5" s="103" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="220">
+      <c r="D5" s="191">
         <f>SUM((INDEX(مرتبات!D1:D1066,H4,1)),VALUE((INDEX(مرتبات!G1:G1066,H4,1))))</f>
-        <v>46300</v>
-      </c>
-      <c r="E5" s="221"/>
-      <c r="F5" s="222"/>
+        <v>0</v>
+      </c>
+      <c r="E5" s="192"/>
+      <c r="F5" s="193"/>
       <c r="G5" s="39"/>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="2:8" ht="13.8" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B6" s="38"/>
-      <c r="C6" s="225" t="s">
+      <c r="C6" s="196" t="s">
         <v>117</v>
       </c>
-      <c r="D6" s="226"/>
-      <c r="E6" s="223" t="s">
+      <c r="D6" s="197"/>
+      <c r="E6" s="194" t="s">
         <v>100</v>
       </c>
-      <c r="F6" s="224"/>
+      <c r="F6" s="195"/>
       <c r="G6" s="39"/>
       <c r="H6" s="5"/>
     </row>
@@ -20052,7 +19923,7 @@
       </c>
       <c r="D11" s="42">
         <f>INDEX(اضافات!J1:J1069,H4,1)</f>
-        <v>10126</v>
+        <v>0</v>
       </c>
       <c r="E11" s="107" t="s">
         <v>114</v>
@@ -20090,7 +19961,7 @@
       </c>
       <c r="D13" s="42">
         <f>INDEX(اضافات!K1:K1069,H4,1)</f>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="E13" s="107" t="s">
         <v>113</v>
@@ -20135,12 +20006,12 @@
       <c r="C16" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="220">
+      <c r="D16" s="191">
         <f>D5+D7+D8+D9+D10+D11+D12+D13</f>
-        <v>57626</v>
-      </c>
-      <c r="E16" s="221"/>
-      <c r="F16" s="222"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="192"/>
+      <c r="F16" s="193"/>
       <c r="G16" s="39"/>
       <c r="H16" s="5"/>
     </row>
@@ -20149,12 +20020,12 @@
       <c r="C17" s="101" t="s">
         <v>123</v>
       </c>
-      <c r="D17" s="211">
+      <c r="D17" s="182">
         <f>SUM(D7:D15)</f>
-        <v>11326</v>
-      </c>
-      <c r="E17" s="212"/>
-      <c r="F17" s="213"/>
+        <v>0</v>
+      </c>
+      <c r="E17" s="183"/>
+      <c r="F17" s="184"/>
       <c r="G17" s="39"/>
       <c r="H17" s="5"/>
     </row>
@@ -20163,12 +20034,12 @@
       <c r="C18" s="102" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="211">
+      <c r="D18" s="182">
         <f>(SUM(F7:F15))</f>
         <v>0</v>
       </c>
-      <c r="E18" s="212"/>
-      <c r="F18" s="213"/>
+      <c r="E18" s="183"/>
+      <c r="F18" s="184"/>
       <c r="G18" s="39"/>
       <c r="H18" s="5"/>
     </row>
@@ -20177,12 +20048,12 @@
       <c r="C19" s="102" t="s">
         <v>101</v>
       </c>
-      <c r="D19" s="214">
+      <c r="D19" s="185">
         <f>D16-D17-D18</f>
-        <v>46300</v>
-      </c>
-      <c r="E19" s="215"/>
-      <c r="F19" s="216"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="186"/>
+      <c r="F19" s="187"/>
       <c r="G19" s="39"/>
       <c r="H19" s="5"/>
     </row>
